--- a/concentration_summary.xlsx
+++ b/concentration_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B3762B-42FC-42C6-A1C3-FB984CB7ADEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89FEF24-39E1-415F-AB54-9C26884DFA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiments" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="180">
   <si>
     <t>Bottle</t>
   </si>
@@ -467,6 +467,117 @@
   </si>
   <si>
     <t xml:space="preserve">Common baseline sample instead? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp Avg </t>
+  </si>
+  <si>
+    <t>Storm Avg</t>
+  </si>
+  <si>
+    <t>Event Avg</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Geom. Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tau_peak </t>
+  </si>
+  <si>
+    <t>Factor of Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">armor </t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>Ln Factor</t>
+  </si>
+  <si>
+    <t>base_tau</t>
+  </si>
+  <si>
+    <t>peak/base</t>
+  </si>
+  <si>
+    <t>peak_tau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOC </t>
   </si>
 </sst>
 </file>
@@ -481,7 +592,7 @@
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,6 +638,20 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -591,7 +716,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -706,12 +831,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1057,16 +1241,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1078,7 +1256,7 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1087,10 +1265,64 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1107,6 +1339,4637 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - All</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>summer storms</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.7385075107143E-2"/>
+                  <c:y val="-0.20312226596675415"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$42:$I$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>71.117321599999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74.728308609999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.767295559999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.631809730000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69.696396059999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$42:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625434987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C260-456E-A562-5835C1ED067A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>spring events</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.0736837598076552E-2"/>
+                  <c:y val="-0.30857465733449985"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$47:$I$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>112.55085055666601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117.49299123</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>115.079453056666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119.222878299999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>115.360934813333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>118.05576815000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>119.77022043333299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125.17995179</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128.631154973333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>127.417386873333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$47:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C260-456E-A562-5835C1ED067A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>experiments</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="lgDashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.31029987063691533"/>
+                  <c:y val="-0.17076006124234472"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$34:$I$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>67.116064212863705</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66.882878692963402</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>66.121917519463807</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.551121204784394</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.281852287603797</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38.708760822076599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.109283772506899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$34:$B$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1507251134754828</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.92680643166171</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C260-456E-A562-5835C1ED067A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - tauc</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.9374937493749375E-2"/>
+                  <c:y val="-0.23629629629629631"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$R$38:$R$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>71.117321599999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74.728308609999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.767295559999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$38:$M$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625434987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8176-405A-B3B2-E62FCF0EC21D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.6785489359746787E-2"/>
+                  <c:y val="-0.2140715223097113"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$R$41:$R$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>115.360934813333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118.05576815000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>119.77022043333299</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128.631154973333</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>127.417386873333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$41:$M$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8176-405A-B3B2-E62FCF0EC21D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="lgDashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.18937515373158936"/>
+                  <c:y val="-0.23760207057451152"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$R$33:$R$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>22.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.992000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.641999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.291</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.274999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$33:$M$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-8176-405A-B3B2-E62FCF0EC21D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - no tauc</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.1044007103413044"/>
+                  <c:y val="-3.348716827063284E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$AA$34:$AA$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>68.631809730000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69.696396059999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$V$34:$V$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7A10-4CCC-8A13-E9933F8BCE21}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.26496865902806499"/>
+                  <c:y val="0.10025262467191601"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$AA$36:$AA$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>112.55085055666601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117.49299123</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>119.222878299999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$V$36:$V$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7A10-4CCC-8A13-E9933F8BCE21}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - All</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.34111362813411239"/>
+                  <c:y val="6.6379529308395774E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$K$42:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$42:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625434987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-845C-4C02-8E84-D9E2495BA71E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.56587690393392909"/>
+                  <c:y val="-0.14097782952209545"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$K$47:$K$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0274951165773749</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0519323679831933</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$47:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-845C-4C02-8E84-D9E2495BA71E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="lgDashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.4077219825208207"/>
+                  <c:y val="0.20997509804712439"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$K$34:$K$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.8217360439061068</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7511459705059222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9502412933524087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1366341811379534</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6045116113513167</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1221084536247956</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2000763085277641</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$B$34:$B$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1507251134754828</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.92680643166171</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-845C-4C02-8E84-D9E2495BA71E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.36681359565398247"/>
+                  <c:y val="-8.3219688422172585E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$77:$I$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.8217360439061068</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7511459705059222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9502412933524087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1366341811379534</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6045116113513167</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1221084536248001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$77:$C$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1507251134754828</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-845C-4C02-8E84-D9E2495BA71E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - with armor</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.14704383888176328"/>
+                  <c:y val="-0.35258556253595119"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$S$38:$S$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$38:$M$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625434987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DF86-4BD0-BCD8-AE272A0C41FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.0503815952550994E-2"/>
+                  <c:y val="-0.28593968080587412"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$S$41:$S$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$41:$M$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DF86-4BD0-BCD8-AE272A0C41FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="lgDashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.218549322118694E-3"/>
+                  <c:y val="0.35818841108970845"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$S$33:$S$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.8217360439061068</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7511459705059222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9502412933524087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1366341811379534</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6045116113513167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$M$33:$M$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-DF86-4BD0-BCD8-AE272A0C41FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Change</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> factor vs Peak Tau - no armor</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.1044007103413044"/>
+                  <c:y val="-3.348716827063284E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$AB$34:$AB$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$V$34:$V$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3633-4FCD-BC58-1E3D58368CA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.43133377611399587"/>
+                  <c:y val="0.18541980303002223"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$AB$36:$AB$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$V$36:$V$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3633-4FCD-BC58-1E3D58368CA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>CF vs peak/base</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Natural Storms</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>natural storms</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.24997267421290081"/>
+                  <c:y val="-7.8431158800185904E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$83:$I$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$83:$C$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1546-4CCC-B685-8671CA96156B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>with armor </c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="dashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.1583515907979233"/>
+                  <c:y val="-0.20031775640632946"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>('Summary '!$I$83:$I$85,'Summary '!$I$91:$I$95)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>('Summary '!$C$83:$C$85,'Summary '!$C$91:$C$95)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1546-4CCC-B685-8671CA96156B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>no armor</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="dashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.48678752866617525"/>
+                  <c:y val="3.5230467519357787E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$I$86:$I$90</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$86:$C$90</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1546-4CCC-B685-8671CA96156B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>CF vs peak/base</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - All</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>with armor </c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="dashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.58088829646316809"/>
+                  <c:y val="-0.19836866195408953"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>('Summary '!$I$77:$I$81,'Summary '!$I$83:$I$85,'Summary '!$I$91:$I$95)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.8217360439061068</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7511459705059222</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9502412933524087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1366341811379534</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6045116113513167</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2053783322033897</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1861636287301587</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2085953872727271</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.039287701021018</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0635654788288289</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0414801776811564</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0809340754061596</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0359137144173414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>('Summary '!$C$77:$C$81,'Summary '!$C$81,'Summary '!$C$83:$C$85,'Summary '!$C$91:$C$95)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>34.051098327464274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.133326116946698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.606836561802155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.672457292115254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>49.604963918585945</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-596B-43C5-93F4-0CC6351B74A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>no armor</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="dashDot"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.48356726305482062"/>
+                  <c:y val="0.17386669237910232"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>('Summary '!$I$82,'Summary '!$I$86:$I$90)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.1221084536248001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0893938052380951</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1062920009523809</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.12550850556666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0878980669444445</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.083844348181809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>('Summary '!$C$82,'Summary '!$C$86:$C$90)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9.1507251134754828</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-596B-43C5-93F4-0CC6351B74A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="25"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>212947</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>188767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>263769</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>74467</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33DC2EF0-FEB6-427F-AE16-47012E03228A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>373672</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>255975</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9A1B15-8806-449A-A69A-6BBAECA4439E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>351692</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>7326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>175380</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>83526</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44B6768E-A99F-4950-9AEF-3C21FD6C1FFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>598790</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>125335</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{672B91A7-EAC9-4019-B5F6-793CBEBE7AC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>708693</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>68970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>490143</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>127069</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6C3587A-C3FB-4D7A-AA4B-6BCB08236167}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>633766</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>133445</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>422155</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>23455</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{229999C7-4B80-4260-B1F4-BA15FB2AB819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>30126</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>85467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>662534</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>177184</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C081314-F542-4EF2-9379-A284E9CFF20F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>46164</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>144998</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>33323</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>46215</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D84F914A-B2C2-4652-8E63-4D257E503320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3590,7 +8453,7 @@
         <v>9.0053213260000007</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" ref="AQ22" si="5">AQ3</f>
+        <f>AQ3</f>
         <v>3.0289999999999999</v>
       </c>
       <c r="AR22" s="9">
@@ -3614,10 +8477,10 @@
       </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="123">
+      <c r="E23" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="F23" s="9">
@@ -3626,19 +8489,19 @@
       <c r="G23" s="9">
         <v>0</v>
       </c>
-      <c r="H23" s="123">
+      <c r="H23" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="J23" s="123">
+      <c r="J23" s="121">
         <v>2.6933749999999996</v>
       </c>
-      <c r="L23" s="122" t="s">
+      <c r="L23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="M23" s="123">
+      <c r="M23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="N23" s="123">
+      <c r="N23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="O23" s="9">
@@ -3647,52 +8510,52 @@
       <c r="P23" s="9">
         <v>0</v>
       </c>
-      <c r="Q23" s="123">
+      <c r="Q23" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="S23" s="122" t="s">
+      <c r="S23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="T23" s="123">
+      <c r="T23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="U23" s="123">
+      <c r="U23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="V23" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="X23" s="122" t="s">
+      <c r="X23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Y23" s="123">
+      <c r="Y23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="Z23" s="123">
+      <c r="Z23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AA23" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AC23" s="122" t="s">
+      <c r="AC23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AD23" s="123">
+      <c r="AD23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="AE23" s="123">
+      <c r="AE23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AF23" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AH23" s="122" t="s">
+      <c r="AH23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AI23" s="123">
+      <c r="AI23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="AJ23" s="123">
+      <c r="AJ23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AK23" s="9">
@@ -3701,28 +8564,28 @@
       <c r="AL23" s="9">
         <v>0</v>
       </c>
-      <c r="AM23" s="123">
+      <c r="AM23" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="AO23" s="122" t="s">
+      <c r="AO23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AP23" s="123">
+      <c r="AP23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="AQ23" s="123">
+      <c r="AQ23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AR23" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AT23" s="122" t="s">
+      <c r="AT23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AU23" s="123">
+      <c r="AU23" s="121">
         <v>4.905691029216193</v>
       </c>
-      <c r="AV23" s="123">
+      <c r="AV23" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AW23" s="9">
@@ -3734,27 +8597,27 @@
         <v>35</v>
       </c>
       <c r="E24" s="18">
-        <f>E20/E22</f>
+        <f t="shared" ref="E24:J24" si="5">E20/E22</f>
         <v>69.484536808026789</v>
       </c>
       <c r="F24" s="18">
-        <f t="shared" ref="F24:I26" si="6">F20/F22</f>
+        <f t="shared" si="5"/>
         <v>35.08352055592956</v>
       </c>
       <c r="G24" s="18">
-        <f>G20/G22</f>
+        <f t="shared" si="5"/>
         <v>46.391649303823002</v>
       </c>
       <c r="H24" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0434782608695652</v>
       </c>
       <c r="I24" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.9333333333333331</v>
       </c>
       <c r="J24" s="18">
-        <f>J20/J22</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K24" s="27"/>
@@ -3762,19 +8625,19 @@
         <v>35</v>
       </c>
       <c r="M24" s="18">
-        <f t="shared" ref="M24:P24" si="7">M20/M22</f>
+        <f>M20/M22</f>
         <v>1</v>
       </c>
       <c r="N24" s="18">
-        <f t="shared" si="7"/>
+        <f>N20/N22</f>
         <v>1</v>
       </c>
       <c r="O24" s="18">
-        <f t="shared" si="7"/>
+        <f>O20/O22</f>
         <v>1.1235564142967069</v>
       </c>
       <c r="P24" s="18">
-        <f t="shared" si="7"/>
+        <f>P20/P22</f>
         <v>2.2250842286109527</v>
       </c>
       <c r="Q24" s="18">
@@ -3785,22 +8648,22 @@
         <v>35</v>
       </c>
       <c r="T24" s="18">
-        <f t="shared" ref="T24:AW24" si="8">T20/T22</f>
+        <f t="shared" ref="T24:AW24" si="6">T20/T22</f>
         <v>7.1228165387102136</v>
       </c>
       <c r="U24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.1070640176600441</v>
       </c>
       <c r="V24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.6182721553469053</v>
       </c>
       <c r="X24" s="17" t="s">
         <v>35</v>
       </c>
       <c r="Y24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.348236588816389</v>
       </c>
       <c r="Z24" s="18">
@@ -3808,75 +8671,75 @@
         <v>1</v>
       </c>
       <c r="AA24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>2.3785855865895376</v>
       </c>
       <c r="AC24" s="17" t="s">
         <v>35</v>
       </c>
       <c r="AD24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>4.0795617822599626</v>
       </c>
       <c r="AE24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.05497022446175</v>
       </c>
       <c r="AF24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>2.9507330689418581</v>
       </c>
       <c r="AH24" s="17" t="s">
         <v>35</v>
       </c>
       <c r="AI24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.916117305452925</v>
       </c>
       <c r="AJ24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.0957810718358039</v>
       </c>
       <c r="AK24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.8987230845870018</v>
       </c>
       <c r="AL24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>2.8884072330938819</v>
       </c>
       <c r="AM24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.1551111695829495</v>
       </c>
       <c r="AO24" s="17" t="s">
         <v>35</v>
       </c>
       <c r="AP24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>4.9849004244182371</v>
       </c>
       <c r="AQ24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.2020468801584683</v>
       </c>
       <c r="AR24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>2.0693920662172096</v>
       </c>
       <c r="AT24" s="17" t="s">
         <v>35</v>
       </c>
       <c r="AU24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>5.1667419110783266</v>
       </c>
       <c r="AV24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.0332893869479236</v>
       </c>
       <c r="AW24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.117863814783858</v>
       </c>
     </row>
@@ -3984,153 +8847,153 @@
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="D26" s="124" t="s">
+      <c r="D26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="125">
+      <c r="E26" s="123">
         <f>E20/E23</f>
         <v>48.941462452511701</v>
       </c>
-      <c r="F26" s="125">
-        <f t="shared" ref="F26:AW26" si="9">F20/F23</f>
+      <c r="F26" s="123">
+        <f t="shared" ref="F26:AW26" si="7">F20/F23</f>
         <v>17.738164848450712</v>
       </c>
-      <c r="G26" s="125" t="e">
+      <c r="G26" s="123" t="e">
         <f>G20/G23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="125">
-        <f t="shared" si="9"/>
+      <c r="H26" s="123">
+        <f t="shared" si="7"/>
         <v>1.4172363497503107</v>
       </c>
-      <c r="I26" s="125" t="e">
-        <f t="shared" si="9"/>
+      <c r="I26" s="123" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J26" s="125">
-        <f t="shared" si="9"/>
+      <c r="J26" s="123">
+        <f t="shared" si="7"/>
         <v>0.78971550563883608</v>
       </c>
-      <c r="L26" s="124" t="s">
+      <c r="L26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="M26" s="125">
-        <f t="shared" si="9"/>
+      <c r="M26" s="123">
+        <f t="shared" si="7"/>
         <v>34.051098327464274</v>
       </c>
-      <c r="N26" s="125">
-        <f t="shared" si="9"/>
+      <c r="N26" s="123">
+        <f t="shared" si="7"/>
         <v>0.98018285608205336</v>
       </c>
-      <c r="O26" s="125">
-        <f t="shared" si="9"/>
+      <c r="O26" s="123">
+        <f t="shared" si="7"/>
         <v>5.6577204597904425</v>
       </c>
-      <c r="P26" s="125" t="e">
-        <f t="shared" si="9"/>
+      <c r="P26" s="123" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q26" s="125">
-        <f t="shared" si="9"/>
+      <c r="Q26" s="123">
+        <f t="shared" si="7"/>
         <v>1.7642466699866741</v>
       </c>
-      <c r="S26" s="124" t="s">
+      <c r="S26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="T26" s="125">
-        <f t="shared" si="9"/>
+      <c r="T26" s="123">
+        <f t="shared" si="7"/>
         <v>33.133326116946698</v>
       </c>
-      <c r="U26" s="125">
-        <f t="shared" si="9"/>
+      <c r="U26" s="123">
+        <f t="shared" si="7"/>
         <v>1.1171856871026129</v>
       </c>
-      <c r="V26" s="125">
-        <f t="shared" si="9"/>
+      <c r="V26" s="123">
+        <f t="shared" si="7"/>
         <v>5.5249844973546773</v>
       </c>
-      <c r="W26" s="125"/>
-      <c r="X26" s="124" t="s">
+      <c r="W26" s="123"/>
+      <c r="X26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="Y26" s="125">
-        <f t="shared" si="9"/>
+      <c r="Y26" s="123">
+        <f t="shared" si="7"/>
         <v>35.606836561802155</v>
       </c>
-      <c r="Z26" s="125">
-        <f t="shared" si="9"/>
+      <c r="Z26" s="123">
+        <f t="shared" si="7"/>
         <v>1.0759734533809813</v>
       </c>
-      <c r="AA26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AA26" s="123">
+        <f t="shared" si="7"/>
         <v>5.0151831509032823</v>
       </c>
-      <c r="AC26" s="124" t="s">
+      <c r="AC26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AD26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AD26" s="123">
+        <f t="shared" si="7"/>
         <v>58.672457292115254</v>
       </c>
-      <c r="AE26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AE26" s="123">
+        <f t="shared" si="7"/>
         <v>0.85506102937763973</v>
       </c>
-      <c r="AF26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AF26" s="123">
+        <f t="shared" si="7"/>
         <v>11.315054026022207</v>
       </c>
-      <c r="AH26" s="124" t="s">
+      <c r="AH26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AI26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AI26" s="123">
+        <f t="shared" si="7"/>
         <v>49.604963918585945</v>
       </c>
-      <c r="AJ26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AJ26" s="123">
+        <f t="shared" si="7"/>
         <v>1.0704042326077878</v>
       </c>
-      <c r="AK26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AK26" s="123">
+        <f t="shared" si="7"/>
         <v>9.5099592815618372</v>
       </c>
-      <c r="AL26" s="125" t="e">
-        <f t="shared" si="9"/>
+      <c r="AL26" s="123" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AM26" s="123">
+        <f t="shared" si="7"/>
         <v>1.5554168938509658</v>
       </c>
-      <c r="AO26" s="124" t="s">
+      <c r="AO26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AP26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AP26" s="123">
+        <f t="shared" si="7"/>
         <v>9.1507251134754828</v>
       </c>
-      <c r="AQ26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AQ26" s="123">
+        <f t="shared" si="7"/>
         <v>1.3518355223464986</v>
       </c>
-      <c r="AR26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AR26" s="123">
+        <f t="shared" si="7"/>
         <v>2.2630995071600584</v>
       </c>
-      <c r="AT26" s="124" t="s">
+      <c r="AT26" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AU26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AU26" s="123">
+        <f t="shared" si="7"/>
         <v>48.92680643166171</v>
       </c>
-      <c r="AV26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AV26" s="123">
+        <f t="shared" si="7"/>
         <v>1.1639671415974382</v>
       </c>
-      <c r="AW26" s="125">
-        <f t="shared" si="9"/>
+      <c r="AW26" s="123">
+        <f t="shared" si="7"/>
         <v>7.8904677790938118</v>
       </c>
     </row>
@@ -5814,252 +10677,252 @@
       </c>
     </row>
     <row r="20" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="123">
+      <c r="B20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="C20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="D20" s="123">
+      <c r="D20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="E20" s="9">
         <v>0</v>
       </c>
-      <c r="F20" s="123">
+      <c r="F20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J20" s="123">
+      <c r="J20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="K20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="L20" s="123">
+      <c r="L20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
-      <c r="N20" s="123">
+      <c r="N20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="Q20" s="122" t="s">
+      <c r="Q20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="R20" s="123">
+      <c r="R20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="S20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="T20" s="123">
+      <c r="T20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="U20" s="9">
         <v>0</v>
       </c>
-      <c r="V20" s="123">
+      <c r="V20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="Y20" s="122" t="s">
+      <c r="Y20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z20" s="123">
+      <c r="Z20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="AA20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AB20" s="123">
+      <c r="AB20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AC20" s="9">
         <v>0</v>
       </c>
-      <c r="AD20" s="123">
+      <c r="AD20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="AG20" s="122" t="s">
+      <c r="AG20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AH20" s="123">
+      <c r="AH20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="AI20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AJ20" s="123">
+      <c r="AJ20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AK20" s="9">
         <v>0</v>
       </c>
-      <c r="AL20" s="123">
+      <c r="AL20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
-      <c r="AO20" s="122" t="s">
+      <c r="AO20" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AP20" s="123">
+      <c r="AP20" s="121">
         <v>4.905691029216193</v>
       </c>
       <c r="AQ20" s="9">
         <v>2.1794107993905221</v>
       </c>
-      <c r="AR20" s="123">
+      <c r="AR20" s="121">
         <v>2.6933749999999996</v>
       </c>
       <c r="AS20" s="9">
         <v>0</v>
       </c>
-      <c r="AT20" s="123">
+      <c r="AT20" s="121">
         <v>1.6934366666666666E-2</v>
       </c>
     </row>
     <row r="21" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A21" s="124" t="s">
+      <c r="A21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="125">
+      <c r="B21" s="123">
         <f>B17/B20</f>
         <v>114.62724202029442</v>
       </c>
-      <c r="C21" s="125">
-        <f t="shared" ref="C21:F21" si="0">C17/C20</f>
+      <c r="C21" s="123">
+        <f>C17/C20</f>
         <v>23.703618328402975</v>
       </c>
-      <c r="D21" s="125">
-        <f t="shared" si="0"/>
+      <c r="D21" s="123">
+        <f>D17/D20</f>
         <v>4.9707151807676251</v>
       </c>
-      <c r="E21" s="125" t="e">
-        <f t="shared" si="0"/>
+      <c r="E21" s="123" t="e">
+        <f>E17/E20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F21" s="125">
-        <f t="shared" si="0"/>
+      <c r="F21" s="123">
+        <f>F17/F20</f>
         <v>5.1965332824178052</v>
       </c>
-      <c r="I21" s="124" t="s">
+      <c r="I21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="125">
+      <c r="J21" s="123">
         <f>J17/J20</f>
         <v>11.767168687113871</v>
       </c>
-      <c r="K21" s="125">
-        <f t="shared" ref="K21" si="1">K17/K20</f>
+      <c r="K21" s="123">
+        <f>K17/K20</f>
         <v>3.112929275118296</v>
       </c>
-      <c r="L21" s="125">
-        <f t="shared" ref="L21" si="2">L17/L20</f>
+      <c r="L21" s="123">
+        <f>L17/L20</f>
         <v>3.2268065159883053</v>
       </c>
-      <c r="M21" s="125" t="e">
-        <f t="shared" ref="M21" si="3">M17/M20</f>
+      <c r="M21" s="123" t="e">
+        <f>M17/M20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N21" s="125">
-        <f t="shared" ref="N21" si="4">N17/N20</f>
+      <c r="N21" s="123">
+        <f>N17/N20</f>
         <v>4.2239902683103985</v>
       </c>
-      <c r="Q21" s="124" t="s">
+      <c r="Q21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="R21" s="125">
+      <c r="R21" s="123">
         <f>R17/R20</f>
         <v>10.007112428555237</v>
       </c>
-      <c r="S21" s="125">
-        <f t="shared" ref="S21" si="5">S17/S20</f>
+      <c r="S21" s="123">
+        <f>S17/S20</f>
         <v>2.4617165630643534</v>
       </c>
-      <c r="T21" s="125">
-        <f t="shared" ref="T21" si="6">T17/T20</f>
+      <c r="T21" s="123">
+        <f>T17/T20</f>
         <v>3.126560542070822</v>
       </c>
-      <c r="U21" s="125" t="e">
-        <f t="shared" ref="U21" si="7">U17/U20</f>
+      <c r="U21" s="123" t="e">
+        <f>U17/U20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V21" s="125">
-        <f t="shared" ref="V21" si="8">V17/V20</f>
+      <c r="V21" s="123">
+        <f>V17/V20</f>
         <v>3.0080723420421198</v>
       </c>
-      <c r="Y21" s="124" t="s">
+      <c r="Y21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="Z21" s="125">
+      <c r="Z21" s="123">
         <f>Z17/Z20</f>
         <v>38.118992591728336</v>
       </c>
-      <c r="AA21" s="125">
-        <f t="shared" ref="AA21" si="9">AA17/AA20</f>
+      <c r="AA21" s="123">
+        <f>AA17/AA20</f>
         <v>13.73910903904674</v>
       </c>
-      <c r="AB21" s="125">
-        <f t="shared" ref="AB21" si="10">AB17/AB20</f>
+      <c r="AB21" s="123">
+        <f>AB17/AB20</f>
         <v>1.9120991321297633</v>
       </c>
-      <c r="AC21" s="125" t="e">
-        <f t="shared" ref="AC21" si="11">AC17/AC20</f>
+      <c r="AC21" s="123" t="e">
+        <f>AC17/AC20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD21" s="125">
-        <f t="shared" ref="AD21" si="12">AD17/AD20</f>
+      <c r="AD21" s="123">
+        <f>AD17/AD20</f>
         <v>4.4701996531707717</v>
       </c>
-      <c r="AG21" s="124" t="s">
+      <c r="AG21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AH21" s="125">
+      <c r="AH21" s="123">
         <f>AH17/AH20</f>
         <v>15.523571643690264</v>
       </c>
-      <c r="AI21" s="125">
-        <f t="shared" ref="AI21" si="13">AI17/AI20</f>
+      <c r="AI21" s="123">
+        <f>AI17/AI20</f>
         <v>3.5687512524154195</v>
       </c>
-      <c r="AJ21" s="125">
-        <f t="shared" ref="AJ21" si="14">AJ17/AJ20</f>
+      <c r="AJ21" s="123">
+        <f>AJ17/AJ20</f>
         <v>1.6607416345662971</v>
       </c>
-      <c r="AK21" s="125" t="e">
-        <f t="shared" ref="AK21" si="15">AK17/AK20</f>
+      <c r="AK21" s="123" t="e">
+        <f>AK17/AK20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL21" s="125">
-        <f t="shared" ref="AL21" si="16">AL17/AL20</f>
+      <c r="AL21" s="123">
+        <f>AL17/AL20</f>
         <v>5.7161866106595856</v>
       </c>
-      <c r="AO21" s="124" t="s">
+      <c r="AO21" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AP21" s="125">
+      <c r="AP21" s="123">
         <f>AP17/AP20</f>
         <v>15.878443297426932</v>
       </c>
-      <c r="AQ21" s="125">
-        <f t="shared" ref="AQ21" si="17">AQ17/AQ20</f>
+      <c r="AQ21" s="123">
+        <f>AQ17/AQ20</f>
         <v>5.8132983192169343</v>
       </c>
-      <c r="AR21" s="125">
-        <f t="shared" ref="AR21" si="18">AR17/AR20</f>
+      <c r="AR21" s="123">
+        <f>AR17/AR20</f>
         <v>1.5883417645147817</v>
       </c>
-      <c r="AS21" s="125" t="e">
-        <f t="shared" ref="AS21" si="19">AS17/AS20</f>
+      <c r="AS21" s="123" t="e">
+        <f>AS17/AS20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT21" s="125">
-        <f t="shared" ref="AT21" si="20">AT17/AT20</f>
+      <c r="AT21" s="123">
+        <f>AT17/AT20</f>
         <v>10.46983353378042</v>
       </c>
     </row>
@@ -7109,14 +11972,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD87D787-BEC8-4379-8C40-73E6824C21FF}">
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:AE131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="117"/>
       <c r="B1" s="115" t="s">
         <v>37</v>
@@ -7133,20 +11999,23 @@
       <c r="F1" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="121" t="s">
+      <c r="G1" s="120" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="121" t="s">
+      <c r="H1" s="120" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="119" t="s">
+      <c r="I1" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="R1" s="119" t="s">
+      <c r="U1" s="20" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="116" t="s">
         <v>117</v>
       </c>
@@ -7165,44 +12034,47 @@
       <c r="F2" s="114">
         <v>1.0434782608695652</v>
       </c>
-      <c r="G2" s="120" t="s">
+      <c r="G2" s="119" t="s">
         <v>133</v>
       </c>
-      <c r="H2" s="120" t="s">
+      <c r="H2" s="119" t="s">
         <v>136</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="I2" s="7"/>
+      <c r="L2" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="115" t="s">
+      <c r="M2" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="115" t="s">
+      <c r="N2" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="115" t="s">
+      <c r="O2" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="115" t="s">
+      <c r="P2" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="115" t="s">
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="U2" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="115" t="s">
+      <c r="V2" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="115" t="s">
+      <c r="W2" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="115" t="s">
+      <c r="X2" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="115" t="s">
+      <c r="Y2" s="115" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="112" t="s">
         <v>118</v>
       </c>
@@ -7227,36 +12099,41 @@
       <c r="H3" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J3" s="112" t="s">
+      <c r="I3" s="5">
+        <v>67.116064212863705</v>
+      </c>
+      <c r="K3" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="110">
+      <c r="L3" s="110">
         <v>7.12281653871021</v>
       </c>
-      <c r="L3" s="110">
+      <c r="M3" s="110">
         <v>3.6182721553469053</v>
       </c>
-      <c r="M3" s="110">
+      <c r="N3" s="110">
         <v>1.1070640176600441</v>
       </c>
-      <c r="N3" s="110"/>
       <c r="O3" s="110"/>
-      <c r="Q3" s="112" t="s">
+      <c r="P3" s="110"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
+      <c r="T3" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="110">
+      <c r="U3" s="110">
         <v>4.9849004244182371</v>
       </c>
-      <c r="S3" s="110">
+      <c r="V3" s="110">
         <v>2.0693920662172096</v>
       </c>
-      <c r="T3" s="110">
+      <c r="W3" s="110">
         <v>1.2020468801584683</v>
       </c>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
+      <c r="X3" s="110"/>
+      <c r="Y3" s="110"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="112" t="s">
         <v>119</v>
       </c>
@@ -7277,38 +12154,43 @@
       <c r="H4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J4" s="112" t="s">
+      <c r="I4" s="5">
+        <v>66.882878692963402</v>
+      </c>
+      <c r="K4" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="K4" s="110">
+      <c r="L4" s="110">
         <v>3.348236588816389</v>
       </c>
-      <c r="L4" s="110">
+      <c r="M4" s="110">
         <v>2.3785855865895376</v>
       </c>
-      <c r="M4" s="110">
+      <c r="N4" s="110">
         <v>1</v>
       </c>
-      <c r="N4" s="110"/>
       <c r="O4" s="110"/>
-      <c r="Q4" s="62" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="T4" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="R4" s="109">
+      <c r="U4" s="109">
         <v>5.7129667032142688</v>
       </c>
-      <c r="S4" s="109">
+      <c r="V4" s="109">
         <v>5.1018819069872396</v>
       </c>
-      <c r="T4" s="109">
+      <c r="W4" s="109">
         <v>1.2961460446247464</v>
       </c>
-      <c r="U4" s="109"/>
-      <c r="V4" s="109">
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109">
         <v>48.925954005559738</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="112" t="s">
         <v>120</v>
       </c>
@@ -7329,38 +12211,43 @@
       <c r="H5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J5" s="112" t="s">
+      <c r="I5" s="5">
+        <v>66.121917519463807</v>
+      </c>
+      <c r="K5" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="K5" s="110">
+      <c r="L5" s="110">
         <v>4.0795617822599626</v>
       </c>
-      <c r="L5" s="110">
+      <c r="M5" s="110">
         <v>2.9507330689418581</v>
       </c>
-      <c r="M5" s="110">
+      <c r="N5" s="110">
         <v>1.05497022446175</v>
       </c>
-      <c r="N5" s="110"/>
       <c r="O5" s="110"/>
-      <c r="Q5" s="62" t="s">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="130"/>
+      <c r="T5" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="R5" s="109">
+      <c r="U5" s="109">
         <v>5.8435661546965711</v>
       </c>
-      <c r="S5" s="109">
+      <c r="V5" s="109">
         <v>8.3106833222568888</v>
       </c>
-      <c r="T5" s="109">
+      <c r="W5" s="109">
         <v>3.8128342245989297</v>
       </c>
-      <c r="U5" s="109"/>
-      <c r="V5" s="109">
+      <c r="X5" s="109"/>
+      <c r="Y5" s="109">
         <v>89.613343442001479</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="112" t="s">
         <v>121</v>
       </c>
@@ -7381,38 +12268,43 @@
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="112" t="s">
+      <c r="I6" s="5">
+        <v>65.551121204784394</v>
+      </c>
+      <c r="K6" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="K6" s="110">
+      <c r="L6" s="110">
         <v>3.916117305452925</v>
       </c>
-      <c r="L6" s="110">
+      <c r="M6" s="110">
         <v>3.8987230845870018</v>
       </c>
-      <c r="M6" s="110">
+      <c r="N6" s="110">
         <v>1.0957810718358039</v>
       </c>
-      <c r="N6" s="110">
+      <c r="O6" s="110">
         <v>2.8884072330938819</v>
       </c>
-      <c r="O6" s="110">
+      <c r="P6" s="110">
         <v>1.1551111695829495</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
+      <c r="T6" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="111">
+      <c r="U6" s="111">
         <v>4.2105263163636364</v>
       </c>
-      <c r="S6" s="118"/>
-      <c r="T6" s="111">
+      <c r="V6" s="118"/>
+      <c r="W6" s="111">
         <v>1.2313167259786477</v>
       </c>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
+      <c r="X6" s="118"/>
+      <c r="Y6" s="118"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="112" t="s">
         <v>122</v>
       </c>
@@ -7437,39 +12329,44 @@
       <c r="H7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="62" t="s">
+      <c r="I7" s="5">
+        <v>67.281852287603797</v>
+      </c>
+      <c r="K7" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="K7" s="109">
+      <c r="L7" s="109">
         <v>19.721931625434987</v>
       </c>
-      <c r="L7" s="109">
+      <c r="M7" s="109">
         <v>3.7276657582042434</v>
       </c>
-      <c r="M7" s="109">
+      <c r="N7" s="109">
         <v>3.099500713266762</v>
       </c>
-      <c r="N7" s="109">
+      <c r="O7" s="109">
         <v>1</v>
       </c>
-      <c r="O7" s="109">
+      <c r="P7" s="109">
         <v>35.765299999999996</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="R7" s="111">
+      <c r="U7" s="111">
         <v>3.0666666666666669</v>
       </c>
-      <c r="S7" s="118"/>
-      <c r="T7" s="111">
+      <c r="V7" s="118"/>
+      <c r="W7" s="111">
         <v>1.0897703549060542</v>
       </c>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
+      <c r="X7" s="118"/>
+      <c r="Y7" s="118"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="112" t="s">
         <v>123</v>
       </c>
@@ -7490,39 +12387,44 @@
       <c r="H8" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="62" t="s">
+      <c r="I8" s="5">
+        <v>38.708760822076599</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="K8" s="109">
+      <c r="L8" s="109">
         <v>16.772053867140858</v>
       </c>
-      <c r="L8" s="109">
+      <c r="M8" s="109">
         <v>3.5296655674874811</v>
       </c>
-      <c r="M8" s="109">
+      <c r="N8" s="109">
         <v>3.0032097004279601</v>
       </c>
-      <c r="N8" s="109">
+      <c r="O8" s="109">
         <v>3.0528906504186062</v>
       </c>
-      <c r="O8" s="109">
+      <c r="P8" s="109">
         <v>25.469899999999999</v>
       </c>
-      <c r="Q8" s="50" t="s">
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
+      <c r="T8" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="R8" s="111">
+      <c r="U8" s="111">
         <v>1.8379446635331478</v>
       </c>
-      <c r="S8" s="118"/>
-      <c r="T8" s="111">
+      <c r="V8" s="118"/>
+      <c r="W8" s="111">
         <v>1.0902620511161436</v>
       </c>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
+      <c r="X8" s="118"/>
+      <c r="Y8" s="118"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="112" t="s">
         <v>124</v>
       </c>
@@ -7543,24 +12445,29 @@
       <c r="H9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J9" s="62" t="s">
+      <c r="I9" s="5">
+        <v>37.109283772506899</v>
+      </c>
+      <c r="K9" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="K9" s="109">
+      <c r="L9" s="109">
         <v>14.025000003506266</v>
       </c>
-      <c r="L9" s="109">
+      <c r="M9" s="109">
         <v>19.641411481675881</v>
       </c>
-      <c r="M9" s="109">
+      <c r="N9" s="109">
         <v>1.8366619115549219</v>
       </c>
-      <c r="N9" s="109"/>
-      <c r="O9" s="109">
+      <c r="O9" s="109"/>
+      <c r="P9" s="109">
         <v>38.261309072529677</v>
       </c>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="62" t="s">
         <v>125</v>
       </c>
@@ -7585,20 +12492,25 @@
       <c r="H10" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J10" s="50" t="s">
+      <c r="I10" s="5">
+        <v>133.4714286</v>
+      </c>
+      <c r="K10" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="111">
+      <c r="L10" s="111">
         <v>1.9732142856297192</v>
       </c>
-      <c r="L10" s="118"/>
-      <c r="M10" s="111">
+      <c r="M10" s="118"/>
+      <c r="N10" s="111">
         <v>1.1892573900504686</v>
       </c>
-      <c r="N10" s="118"/>
       <c r="O10" s="118"/>
+      <c r="P10" s="118"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" s="132"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="62" t="s">
         <v>126</v>
       </c>
@@ -7623,20 +12535,25 @@
       <c r="H11" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="I11" s="5">
+        <v>71.117321599999997</v>
+      </c>
+      <c r="K11" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="K11" s="111">
+      <c r="L11" s="111">
         <v>2.3771106941838647</v>
       </c>
-      <c r="L11" s="118"/>
-      <c r="M11" s="111">
+      <c r="M11" s="118"/>
+      <c r="N11" s="111">
         <v>1.1846386681800984</v>
       </c>
-      <c r="N11" s="118"/>
       <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="132"/>
+      <c r="R11" s="132"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="62" t="s">
         <v>127</v>
       </c>
@@ -7661,20 +12578,25 @@
       <c r="H12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J12" s="50" t="s">
+      <c r="I12" s="5">
+        <v>74.728308609999999</v>
+      </c>
+      <c r="K12" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="K12" s="111">
+      <c r="L12" s="111">
         <v>4.4800000000000004</v>
       </c>
-      <c r="L12" s="118"/>
-      <c r="M12" s="111">
+      <c r="M12" s="118"/>
+      <c r="N12" s="111">
         <v>1.3070266528210455</v>
       </c>
-      <c r="N12" s="118"/>
       <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" s="132"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
         <v>128</v>
       </c>
@@ -7697,22 +12619,27 @@
       <c r="H13" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J13" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" s="111">
-        <v>1</v>
-      </c>
-      <c r="L13" s="118"/>
-      <c r="M13" s="111">
-        <v>1.047928791509757</v>
-      </c>
-      <c r="N13" s="118"/>
+      <c r="I13" s="5">
+        <v>79.767295559999994</v>
+      </c>
+      <c r="K13" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="111">
+        <v>7.2333333348616673</v>
+      </c>
+      <c r="M13" s="118"/>
+      <c r="N13" s="111">
+        <v>1.2011631885049607</v>
+      </c>
       <c r="O13" s="118"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="132"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>129</v>
       </c>
@@ -7735,22 +12662,27 @@
       <c r="H14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J14" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" s="111">
-        <v>7.2333333348616673</v>
-      </c>
-      <c r="L14" s="118"/>
-      <c r="M14" s="111">
-        <v>1.2011631885049607</v>
-      </c>
-      <c r="N14" s="118"/>
+      <c r="I14" s="5">
+        <v>68.631809730000001</v>
+      </c>
+      <c r="K14" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="111">
+        <v>1.9999999997857143</v>
+      </c>
+      <c r="M14" s="118"/>
+      <c r="N14" s="111">
+        <v>1.115581316058643</v>
+      </c>
       <c r="O14" s="118"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="132"/>
+      <c r="R14" s="132"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="62" t="s">
         <v>130</v>
       </c>
@@ -7773,20 +12705,11 @@
       <c r="H15" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J15" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="K15" s="111">
-        <v>1.9999999997857143</v>
-      </c>
-      <c r="L15" s="118"/>
-      <c r="M15" s="111">
-        <v>1.115581316058643</v>
-      </c>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
+      <c r="I15" s="5">
+        <v>69.696396059999998</v>
+      </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
         <v>101</v>
       </c>
@@ -7805,8 +12728,11 @@
       <c r="H16" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I16" s="5">
+        <v>112.55085055666601</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
         <v>102</v>
       </c>
@@ -7825,52 +12751,57 @@
       <c r="H17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J17" s="122" t="s">
+      <c r="I17" s="5">
+        <v>117.49299123</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="K17" s="9">
-        <f>AVERAGE(K3:K15)</f>
-        <v>6.7730289250601983</v>
-      </c>
       <c r="L17" s="9">
-        <f t="shared" ref="L17:O17" si="0">AVERAGE(L3:L15)</f>
+        <f>AVERAGE(L3:L14)</f>
+        <v>7.2541146688152152</v>
+      </c>
+      <c r="M17" s="9">
+        <f>AVERAGE(M3:M14)</f>
         <v>5.6778652432618442</v>
       </c>
-      <c r="M17" s="9">
-        <f t="shared" si="0"/>
-        <v>1.4802141266409394</v>
-      </c>
       <c r="N17" s="9">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(N3:N14)</f>
+        <v>1.5162379045685384</v>
+      </c>
+      <c r="O17" s="9">
+        <f>AVERAGE(O3:O14)</f>
         <v>2.3137659611708297</v>
       </c>
-      <c r="O17" s="9">
-        <f t="shared" si="0"/>
+      <c r="P17" s="9">
+        <f>AVERAGE(P3:P14)</f>
         <v>25.162905060528153</v>
       </c>
-      <c r="Q17" s="122" t="s">
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="T17" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="R17" s="9">
-        <f>AVERAGE(R3:R8)</f>
+      <c r="U17" s="9">
+        <f>AVERAGE(U3:U8)</f>
         <v>4.2760951548154216</v>
       </c>
-      <c r="S17" s="9">
-        <f t="shared" ref="S17:V17" si="1">AVERAGE(S3:S8)</f>
+      <c r="V17" s="9">
+        <f>AVERAGE(V3:V8)</f>
         <v>5.1606524318204459</v>
       </c>
-      <c r="T17" s="9">
-        <f t="shared" si="1"/>
+      <c r="W17" s="9">
+        <f>AVERAGE(W3:W8)</f>
         <v>1.620396046897165</v>
       </c>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9">
-        <f t="shared" si="1"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9">
+        <f>AVERAGE(Y3:Y8)</f>
         <v>69.269648723780605</v>
       </c>
-      <c r="W17" s="7"/>
+      <c r="Z17" s="7"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="50" t="s">
         <v>103</v>
       </c>
@@ -7889,8 +12820,31 @@
       <c r="H18" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I18" s="5">
+        <v>115.079453056666</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="L18" s="7">
+        <v>12</v>
+      </c>
+      <c r="M18" s="7">
+        <v>7</v>
+      </c>
+      <c r="N18" s="7">
+        <v>12</v>
+      </c>
+      <c r="O18" s="7">
+        <v>3</v>
+      </c>
+      <c r="P18" s="7">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
         <v>104</v>
       </c>
@@ -7909,8 +12863,11 @@
       <c r="H19" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I19" s="5">
+        <v>119.222878299999</v>
+      </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
         <v>105</v>
       </c>
@@ -7929,8 +12886,54 @@
       <c r="H20" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I20" s="5">
+        <v>115.360934813333</v>
+      </c>
+      <c r="K20" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" s="9">
+        <f>AVERAGE(L3:L6)</f>
+        <v>4.6166830538098713</v>
+      </c>
+      <c r="M20" s="9">
+        <f>AVERAGE(M3:M6)</f>
+        <v>3.211578473866326</v>
+      </c>
+      <c r="N20" s="9">
+        <f>AVERAGE(N3:N6)</f>
+        <v>1.0644538284893996</v>
+      </c>
+      <c r="O20" s="9">
+        <f>AVERAGE(O3:O6)</f>
+        <v>2.8884072330938819</v>
+      </c>
+      <c r="P20" s="9">
+        <f>AVERAGE(P3:P6)</f>
+        <v>1.1551111695829495</v>
+      </c>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" t="s">
+        <v>143</v>
+      </c>
+      <c r="U20" s="9">
+        <f>AVERAGE(U3)</f>
+        <v>4.9849004244182371</v>
+      </c>
+      <c r="V20" s="9">
+        <f>AVERAGE(V3)</f>
+        <v>2.0693920662172096</v>
+      </c>
+      <c r="W20" s="9">
+        <f>AVERAGE(W3)</f>
+        <v>1.2020468801584683</v>
+      </c>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
         <v>106</v>
       </c>
@@ -7949,8 +12952,56 @@
       <c r="H21" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I21" s="5">
+        <v>118.05576815000001</v>
+      </c>
+      <c r="K21" t="s">
+        <v>144</v>
+      </c>
+      <c r="L21" s="9">
+        <f>AVERAGE(L7:L9)</f>
+        <v>16.839661832027371</v>
+      </c>
+      <c r="M21" s="9">
+        <f>AVERAGE(M7:M9)</f>
+        <v>8.9662476024558675</v>
+      </c>
+      <c r="N21" s="9">
+        <f>AVERAGE(N7:N9)</f>
+        <v>2.6464574417498814</v>
+      </c>
+      <c r="O21" s="9">
+        <f>AVERAGE(O7:O9)</f>
+        <v>2.0264453252093029</v>
+      </c>
+      <c r="P21" s="9">
+        <f>AVERAGE(P7:P9)</f>
+        <v>33.165503024176559</v>
+      </c>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="T21" t="s">
+        <v>144</v>
+      </c>
+      <c r="U21" s="9">
+        <f>AVERAGE(U4:U5)</f>
+        <v>5.77826642895542</v>
+      </c>
+      <c r="V21" s="9">
+        <f>AVERAGE(V4:V5)</f>
+        <v>6.7062826146220642</v>
+      </c>
+      <c r="W21" s="9">
+        <f>AVERAGE(W4:W5)</f>
+        <v>2.554490134611838</v>
+      </c>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9">
+        <f>AVERAGE(Y4:Y5)</f>
+        <v>69.269648723780605</v>
+      </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="50" t="s">
         <v>107</v>
       </c>
@@ -7969,8 +13020,41 @@
       <c r="H22" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I22" s="5">
+        <v>119.77022043333299</v>
+      </c>
+      <c r="K22" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="9">
+        <f>AVERAGE(L10:L14)</f>
+        <v>3.6127316628921933</v>
+      </c>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9">
+        <f>AVERAGE(N10:N14)</f>
+        <v>1.1995334431230433</v>
+      </c>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="T22" t="s">
+        <v>145</v>
+      </c>
+      <c r="U22" s="9">
+        <f>AVERAGE(U6:U8)</f>
+        <v>3.0383792155211502</v>
+      </c>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9">
+        <f>AVERAGE(W6:W8)</f>
+        <v>1.137116377333615</v>
+      </c>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
         <v>108</v>
       </c>
@@ -7989,8 +13073,11 @@
       <c r="H23" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I23" s="5">
+        <v>125.17995179</v>
+      </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
         <v>109</v>
       </c>
@@ -8009,8 +13096,11 @@
       <c r="H24" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I24" s="5">
+        <v>128.631154973333</v>
+      </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>116</v>
       </c>
@@ -8029,89 +13119,180 @@
       <c r="H25" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I25" s="5">
+        <v>127.417386873333</v>
+      </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>142</v>
       </c>
+      <c r="M31" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="V31" s="20" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="117"/>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="128" t="s">
+      <c r="C32" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="128" t="s">
+      <c r="D32" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="128" t="s">
+      <c r="E32" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="128" t="s">
+      <c r="F32" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="121" t="s">
+      <c r="G32" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="H32" s="126" t="s">
+      <c r="H32" s="124" t="s">
         <v>132</v>
       </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
+      <c r="I32" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="M32" s="115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="O32" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="P32" s="115" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q32" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="V32" s="115" t="s">
+        <v>37</v>
+      </c>
+      <c r="W32" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="X32" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y32" s="115" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z32" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA32" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB32" s="20" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="129">
+      <c r="B33" s="127">
         <v>48.941462452511701</v>
       </c>
-      <c r="C33" s="129">
+      <c r="C33" s="127">
         <v>17.738164848450712</v>
       </c>
-      <c r="D33" s="129">
+      <c r="D33" s="127">
         <v>0.78971550563883608</v>
       </c>
       <c r="E33" s="110"/>
-      <c r="F33" s="129">
+      <c r="F33" s="127">
         <v>1.4172363497503107</v>
       </c>
-      <c r="G33" s="120" t="s">
+      <c r="G33" s="119" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="120" t="s">
+      <c r="H33" s="119" t="s">
         <v>136</v>
       </c>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
+      <c r="I33" s="7"/>
+      <c r="L33" s="112" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="127">
+        <v>34.051098327464274</v>
+      </c>
+      <c r="N33" s="127">
+        <v>5.6577204597904425</v>
+      </c>
+      <c r="O33" s="127">
+        <v>0.98018285608205336</v>
+      </c>
+      <c r="P33" s="110"/>
+      <c r="Q33" s="127">
+        <v>1.7642466699866741</v>
+      </c>
+      <c r="R33" s="129">
+        <v>22.75</v>
+      </c>
+      <c r="S33" s="9">
+        <f>K34</f>
+        <v>1.8217360439061068</v>
+      </c>
+      <c r="U33" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="V33" s="127">
+        <v>9.1507251134754828</v>
+      </c>
+      <c r="W33" s="127">
+        <v>2.2630995071600584</v>
+      </c>
+      <c r="X33" s="127">
+        <v>1.3518355223464986</v>
+      </c>
+      <c r="Y33" s="110"/>
+      <c r="Z33" s="110"/>
+      <c r="AA33" s="129">
+        <v>10.617000000000001</v>
+      </c>
+      <c r="AB33" s="16">
+        <f>K39</f>
+        <v>1.1221084536247956</v>
+      </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="129">
+      <c r="B34" s="127">
         <v>34.051098327464274</v>
       </c>
-      <c r="C34" s="129">
+      <c r="C34" s="127">
         <v>5.6577204597904425</v>
       </c>
-      <c r="D34" s="129">
+      <c r="D34" s="127">
         <v>0.98018285608205336</v>
       </c>
       <c r="E34" s="110"/>
-      <c r="F34" s="129">
+      <c r="F34" s="127">
         <v>1.7642466699866741</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -8120,23 +13301,72 @@
       <c r="H34" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
+      <c r="I34" s="5">
+        <v>67.116064212863705</v>
+      </c>
+      <c r="J34" s="9">
+        <v>36.841816045400101</v>
+      </c>
+      <c r="K34" s="9">
+        <f>I34/J34</f>
+        <v>1.8217360439061068</v>
+      </c>
+      <c r="L34" s="112" t="s">
+        <v>119</v>
+      </c>
+      <c r="M34" s="127">
+        <v>33.133326116946698</v>
+      </c>
+      <c r="N34" s="127">
+        <v>5.5249844973546773</v>
+      </c>
+      <c r="O34" s="127">
+        <v>1.1171856871026129</v>
+      </c>
+      <c r="P34" s="110"/>
+      <c r="Q34" s="110"/>
+      <c r="R34" s="5">
+        <v>21.992000000000001</v>
+      </c>
+      <c r="S34" s="9">
+        <f>K35</f>
+        <v>1.7511459705059222</v>
+      </c>
+      <c r="U34" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="V34" s="109">
+        <v>5.7129667032142688</v>
+      </c>
+      <c r="W34" s="109">
+        <v>5.1018819069872396</v>
+      </c>
+      <c r="X34" s="109">
+        <v>1.2961460446247464</v>
+      </c>
+      <c r="Y34" s="109"/>
+      <c r="Z34" s="109">
+        <v>48.925954005559738</v>
+      </c>
+      <c r="AA34" s="5">
+        <v>68.631809730000001</v>
+      </c>
+      <c r="AB34" s="133">
+        <f>K45</f>
+        <v>1.0893938052380951</v>
+      </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="129">
+      <c r="B35" s="127">
         <v>33.133326116946698</v>
       </c>
-      <c r="C35" s="129">
+      <c r="C35" s="127">
         <v>5.5249844973546773</v>
       </c>
-      <c r="D35" s="129">
+      <c r="D35" s="127">
         <v>1.1171856871026129</v>
       </c>
       <c r="E35" s="110"/>
@@ -8147,21 +13377,72 @@
       <c r="H35" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
+      <c r="I35" s="5">
+        <v>66.882878692963402</v>
+      </c>
+      <c r="J35" s="9">
+        <v>38.193777000577697</v>
+      </c>
+      <c r="K35" s="9">
+        <f t="shared" ref="K35:K55" si="0">I35/J35</f>
+        <v>1.7511459705059222</v>
+      </c>
+      <c r="L35" s="112" t="s">
+        <v>120</v>
+      </c>
+      <c r="M35" s="127">
+        <v>35.606836561802155</v>
+      </c>
+      <c r="N35" s="127">
+        <v>5.0151831509032823</v>
+      </c>
+      <c r="O35" s="127">
+        <v>1.0759734533809813</v>
+      </c>
+      <c r="P35" s="110"/>
+      <c r="Q35" s="110"/>
+      <c r="R35" s="5">
+        <v>21.641999999999999</v>
+      </c>
+      <c r="S35" s="9">
+        <f>K36</f>
+        <v>1.9502412933524087</v>
+      </c>
+      <c r="U35" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="V35" s="109">
+        <v>5.8435661546965711</v>
+      </c>
+      <c r="W35" s="109">
+        <v>8.3106833222568888</v>
+      </c>
+      <c r="X35" s="109">
+        <v>3.8128342245989297</v>
+      </c>
+      <c r="Y35" s="109"/>
+      <c r="Z35" s="109">
+        <v>89.613343442001479</v>
+      </c>
+      <c r="AA35" s="5">
+        <v>69.696396059999998</v>
+      </c>
+      <c r="AB35" s="133">
+        <f>K46</f>
+        <v>1.1062920009523809</v>
+      </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="129">
+      <c r="B36" s="127">
         <v>35.606836561802155</v>
       </c>
-      <c r="C36" s="129">
+      <c r="C36" s="127">
         <v>5.0151831509032823</v>
       </c>
-      <c r="D36" s="129">
+      <c r="D36" s="127">
         <v>1.0759734533809813</v>
       </c>
       <c r="E36" s="110"/>
@@ -8172,21 +13453,71 @@
       <c r="H36" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I36" s="5">
+        <v>66.121917519463807</v>
+      </c>
+      <c r="J36" s="9">
+        <v>33.904480304486903</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="shared" si="0"/>
+        <v>1.9502412933524087</v>
+      </c>
+      <c r="L36" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="M36" s="127">
+        <v>58.672457292115254</v>
+      </c>
+      <c r="N36" s="127">
+        <v>11.315054026022207</v>
+      </c>
+      <c r="O36" s="127">
+        <v>0.85506102937763973</v>
+      </c>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="110"/>
+      <c r="R36" s="5">
+        <v>21.291</v>
+      </c>
+      <c r="S36" s="9">
+        <f>K37</f>
+        <v>2.1366341811379534</v>
+      </c>
+      <c r="U36" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="V36" s="111">
+        <v>4.2105263163636364</v>
+      </c>
+      <c r="W36" s="118"/>
+      <c r="X36" s="111">
+        <v>1.2313167259786477</v>
+      </c>
+      <c r="Y36" s="118"/>
+      <c r="Z36" s="118"/>
+      <c r="AA36" s="5">
+        <v>112.55085055666601</v>
+      </c>
+      <c r="AB36" s="16">
+        <f>K47</f>
+        <v>1.12550850556666</v>
+      </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="129">
+      <c r="B37" s="127">
         <v>58.672457292115254</v>
       </c>
-      <c r="C37" s="129">
+      <c r="C37" s="127">
         <v>11.315054026022207</v>
       </c>
-      <c r="D37" s="129">
+      <c r="D37" s="127">
         <v>0.85506102937763973</v>
       </c>
-      <c r="E37" s="130"/>
+      <c r="E37" s="128"/>
       <c r="F37" s="110"/>
       <c r="G37" s="2" t="s">
         <v>133</v>
@@ -8194,22 +13525,75 @@
       <c r="H37" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I37" s="5">
+        <v>65.551121204784394</v>
+      </c>
+      <c r="J37" s="9">
+        <v>30.6796183377879</v>
+      </c>
+      <c r="K37" s="9">
+        <f t="shared" si="0"/>
+        <v>2.1366341811379534</v>
+      </c>
+      <c r="L37" s="112" t="s">
+        <v>122</v>
+      </c>
+      <c r="M37" s="127">
+        <v>49.604963918585945</v>
+      </c>
+      <c r="N37" s="127">
+        <v>9.5099592815618372</v>
+      </c>
+      <c r="O37" s="127">
+        <v>1.0704042326077878</v>
+      </c>
+      <c r="P37" s="110"/>
+      <c r="Q37" s="127">
+        <v>1.5554168938509658</v>
+      </c>
+      <c r="R37" s="129">
+        <v>23.274999999999999</v>
+      </c>
+      <c r="S37" s="9">
+        <f>K38</f>
+        <v>2.6045116113513167</v>
+      </c>
+      <c r="T37" s="7"/>
+      <c r="U37" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="V37" s="111">
+        <v>3.0666666666666669</v>
+      </c>
+      <c r="W37" s="118"/>
+      <c r="X37" s="111">
+        <v>1.0897703549060542</v>
+      </c>
+      <c r="Y37" s="118"/>
+      <c r="Z37" s="118"/>
+      <c r="AA37" s="5">
+        <v>117.49299123</v>
+      </c>
+      <c r="AB37" s="16">
+        <f>K48</f>
+        <v>1.0878980669444445</v>
+      </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="129">
+      <c r="B38" s="127">
         <v>49.604963918585945</v>
       </c>
-      <c r="C38" s="129">
+      <c r="C38" s="127">
         <v>9.5099592815618372</v>
       </c>
-      <c r="D38" s="129">
+      <c r="D38" s="127">
         <v>1.0704042326077878</v>
       </c>
       <c r="E38" s="110"/>
-      <c r="F38" s="129">
+      <c r="F38" s="127">
         <v>1.5554168938509658</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -8218,18 +13602,72 @@
       <c r="H38" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I38" s="5">
+        <v>67.281852287603797</v>
+      </c>
+      <c r="J38" s="9">
+        <v>25.832809496554901</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="shared" si="0"/>
+        <v>2.6045116113513167</v>
+      </c>
+      <c r="L38" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="M38" s="109">
+        <v>19.721931625434987</v>
+      </c>
+      <c r="N38" s="109">
+        <v>3.7276657582042434</v>
+      </c>
+      <c r="O38" s="109">
+        <v>3.099500713266762</v>
+      </c>
+      <c r="P38" s="109">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="109">
+        <v>35.765299999999996</v>
+      </c>
+      <c r="R38" s="5">
+        <v>71.117321599999997</v>
+      </c>
+      <c r="S38" s="9">
+        <f>K42</f>
+        <v>1.2053783322033897</v>
+      </c>
+      <c r="U38" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="V38" s="111">
+        <v>1.8379446635331478</v>
+      </c>
+      <c r="W38" s="118"/>
+      <c r="X38" s="111">
+        <v>1.0902620511161436</v>
+      </c>
+      <c r="Y38" s="118"/>
+      <c r="Z38" s="118"/>
+      <c r="AA38" s="5">
+        <v>119.222878299999</v>
+      </c>
+      <c r="AB38" s="16">
+        <f>K50</f>
+        <v>1.083844348181809</v>
+      </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="129">
+      <c r="B39" s="127">
         <v>9.1507251134754828</v>
       </c>
-      <c r="C39" s="129">
+      <c r="C39" s="127">
         <v>2.2630995071600584</v>
       </c>
-      <c r="D39" s="129">
+      <c r="D39" s="127">
         <v>1.3518355223464986</v>
       </c>
       <c r="E39" s="110"/>
@@ -8240,18 +13678,53 @@
       <c r="H39" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I39" s="5">
+        <v>38.708760822076599</v>
+      </c>
+      <c r="J39" s="9">
+        <v>34.496452367891898</v>
+      </c>
+      <c r="K39" s="9">
+        <f t="shared" si="0"/>
+        <v>1.1221084536247956</v>
+      </c>
+      <c r="L39" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="M39" s="109">
+        <v>16.772053867140858</v>
+      </c>
+      <c r="N39" s="109">
+        <v>3.5296655674874811</v>
+      </c>
+      <c r="O39" s="109">
+        <v>3.0032097004279601</v>
+      </c>
+      <c r="P39" s="109">
+        <v>3.0528906504186062</v>
+      </c>
+      <c r="Q39" s="109">
+        <v>25.469899999999999</v>
+      </c>
+      <c r="R39" s="5">
+        <v>74.728308609999999</v>
+      </c>
+      <c r="S39" s="9">
+        <f>K43</f>
+        <v>1.1861636287301587</v>
+      </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="112" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="129">
+      <c r="B40" s="127">
         <v>48.92680643166171</v>
       </c>
-      <c r="C40" s="129">
+      <c r="C40" s="127">
         <v>7.8904677790938118</v>
       </c>
-      <c r="D40" s="129">
+      <c r="D40" s="127">
         <v>1.1639671415974382</v>
       </c>
       <c r="E40" s="110"/>
@@ -8262,26 +13735,58 @@
       <c r="H40" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
+      <c r="I40" s="5">
+        <v>37.109283772506899</v>
+      </c>
+      <c r="J40" s="9">
+        <v>30.9224367724016</v>
+      </c>
+      <c r="K40" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2000763085277641</v>
+      </c>
+      <c r="L40" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="M40" s="109">
+        <v>14.025000003506266</v>
+      </c>
+      <c r="N40" s="109">
+        <v>19.641411481675881</v>
+      </c>
+      <c r="O40" s="109">
+        <v>1.8366619115549219</v>
+      </c>
+      <c r="P40" s="109"/>
+      <c r="Q40" s="109">
+        <v>38.261309072529677</v>
+      </c>
+      <c r="R40" s="5">
+        <v>79.767295559999994</v>
+      </c>
+      <c r="S40" s="9">
+        <f>K44</f>
+        <v>1.2085953872727271</v>
+      </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="B41" s="129">
-        <v>114.62724202029442</v>
-      </c>
-      <c r="C41" s="129">
-        <v>23.703618328402975</v>
-      </c>
-      <c r="D41" s="129">
-        <v>4.9707151807676251</v>
-      </c>
-      <c r="E41" s="129"/>
-      <c r="F41" s="129">
-        <v>5.1965332824178052</v>
+      <c r="B41" s="109">
+        <v>127.52410844439085</v>
+      </c>
+      <c r="C41" s="109">
+        <v>18.033647569042632</v>
+      </c>
+      <c r="D41" s="109">
+        <v>7.6328392246294188</v>
+      </c>
+      <c r="E41" s="109">
+        <v>1.3691924906768826</v>
+      </c>
+      <c r="F41" s="109">
+        <v>3.3523809523809525</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>133</v>
@@ -8289,23 +13794,54 @@
       <c r="H41" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="I41" s="5">
+        <v>133.4714286</v>
+      </c>
+      <c r="J41" s="9">
+        <v>70</v>
+      </c>
+      <c r="K41" s="9">
+        <f t="shared" si="0"/>
+        <v>1.9067346942857142</v>
+      </c>
+      <c r="L41" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="M41" s="111">
+        <v>1.9732142856297192</v>
+      </c>
+      <c r="N41" s="118"/>
+      <c r="O41" s="111">
+        <v>1.1892573900504686</v>
+      </c>
+      <c r="P41" s="118"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="5">
+        <v>115.360934813333</v>
+      </c>
+      <c r="S41" s="9">
+        <f>K51</f>
+        <v>1.039287701021018</v>
+      </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="B42" s="129">
-        <v>11.767168687113871</v>
-      </c>
-      <c r="C42" s="129">
-        <v>3.112929275118296</v>
-      </c>
-      <c r="D42" s="129">
-        <v>3.2268065159883053</v>
-      </c>
-      <c r="E42" s="129"/>
-      <c r="F42" s="129">
-        <v>4.2239902683103985</v>
+      <c r="B42" s="109">
+        <v>19.721931625434987</v>
+      </c>
+      <c r="C42" s="109">
+        <v>3.7276657582042434</v>
+      </c>
+      <c r="D42" s="109">
+        <v>3.099500713266762</v>
+      </c>
+      <c r="E42" s="109">
+        <v>1</v>
+      </c>
+      <c r="F42" s="109">
+        <v>35.765299999999996</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>133</v>
@@ -8313,23 +13849,54 @@
       <c r="H42" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I42" s="5">
+        <v>71.117321599999997</v>
+      </c>
+      <c r="J42" s="9">
+        <v>59</v>
+      </c>
+      <c r="K42" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2053783322033897</v>
+      </c>
+      <c r="L42" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="M42" s="111">
+        <v>2.3771106941838647</v>
+      </c>
+      <c r="N42" s="118"/>
+      <c r="O42" s="111">
+        <v>1.1846386681800984</v>
+      </c>
+      <c r="P42" s="118"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="5">
+        <v>118.05576815000001</v>
+      </c>
+      <c r="S42" s="9">
+        <f>K52</f>
+        <v>1.0635654788288289</v>
+      </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B43" s="129">
-        <v>10.007112428555237</v>
-      </c>
-      <c r="C43" s="129">
-        <v>2.4617165630643534</v>
-      </c>
-      <c r="D43" s="129">
-        <v>3.126560542070822</v>
-      </c>
-      <c r="E43" s="129"/>
-      <c r="F43" s="129">
-        <v>3.0080723420421198</v>
+      <c r="B43" s="109">
+        <v>16.772053867140858</v>
+      </c>
+      <c r="C43" s="109">
+        <v>3.5296655674874811</v>
+      </c>
+      <c r="D43" s="109">
+        <v>3.0032097004279601</v>
+      </c>
+      <c r="E43" s="109">
+        <v>3.0528906504186062</v>
+      </c>
+      <c r="F43" s="109">
+        <v>25.469899999999999</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>133</v>
@@ -8337,23 +13904,54 @@
       <c r="H43" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I43" s="5">
+        <v>74.728308609999999</v>
+      </c>
+      <c r="J43" s="9">
+        <v>63</v>
+      </c>
+      <c r="K43" s="9">
+        <f t="shared" si="0"/>
+        <v>1.1861636287301587</v>
+      </c>
+      <c r="L43" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="M43" s="111">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="N43" s="118"/>
+      <c r="O43" s="111">
+        <v>1.3070266528210455</v>
+      </c>
+      <c r="P43" s="118"/>
+      <c r="Q43" s="118"/>
+      <c r="R43" s="5">
+        <v>119.77022043333299</v>
+      </c>
+      <c r="S43" s="9">
+        <f>K53</f>
+        <v>1.0414801776811564</v>
+      </c>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="129">
-        <v>38.118992591728336</v>
-      </c>
-      <c r="C44" s="129">
-        <v>13.73910903904674</v>
-      </c>
-      <c r="D44" s="129">
-        <v>1.9120991321297633</v>
-      </c>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129">
-        <v>4.4701996531707717</v>
+      <c r="B44" s="109">
+        <v>14.025000003506266</v>
+      </c>
+      <c r="C44" s="109">
+        <v>19.641411481675881</v>
+      </c>
+      <c r="D44" s="109">
+        <v>1.8366619115549219</v>
+      </c>
+      <c r="E44" s="109"/>
+      <c r="F44" s="109">
+        <v>38.261309072529677</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>133</v>
@@ -8361,23 +13959,54 @@
       <c r="H44" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I44" s="5">
+        <v>79.767295559999994</v>
+      </c>
+      <c r="J44" s="9">
+        <v>66</v>
+      </c>
+      <c r="K44" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2085953872727271</v>
+      </c>
+      <c r="L44" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="M44" s="111">
+        <v>7.2333333348616673</v>
+      </c>
+      <c r="N44" s="118"/>
+      <c r="O44" s="111">
+        <v>1.2011631885049607</v>
+      </c>
+      <c r="P44" s="118"/>
+      <c r="Q44" s="118"/>
+      <c r="R44" s="5">
+        <v>128.631154973333</v>
+      </c>
+      <c r="S44" s="9">
+        <f>K55</f>
+        <v>1.0809340754061596</v>
+      </c>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="129">
-        <v>15.523571643690264</v>
-      </c>
-      <c r="C45" s="129">
-        <v>3.5687512524154195</v>
-      </c>
-      <c r="D45" s="129">
-        <v>1.6607416345662971</v>
-      </c>
-      <c r="E45" s="129"/>
-      <c r="F45" s="129">
-        <v>5.7161866106595856</v>
+      <c r="B45" s="109">
+        <v>5.7129667032142688</v>
+      </c>
+      <c r="C45" s="109">
+        <v>5.1018819069872396</v>
+      </c>
+      <c r="D45" s="109">
+        <v>1.2961460446247464</v>
+      </c>
+      <c r="E45" s="109"/>
+      <c r="F45" s="109">
+        <v>48.925954005559738</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>133</v>
@@ -8385,23 +14014,52 @@
       <c r="H45" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I45" s="5">
+        <v>68.631809730000001</v>
+      </c>
+      <c r="J45" s="9">
+        <v>63</v>
+      </c>
+      <c r="K45" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0893938052380951</v>
+      </c>
+      <c r="L45" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="M45" s="111">
+        <v>1.9999999997857143</v>
+      </c>
+      <c r="N45" s="118"/>
+      <c r="O45" s="111">
+        <v>1.115581316058643</v>
+      </c>
+      <c r="P45" s="118"/>
+      <c r="Q45" s="118"/>
+      <c r="R45" s="5">
+        <v>127.417386873333</v>
+      </c>
+      <c r="S45" s="9">
+        <f>K56</f>
+        <v>1.0359137144173414</v>
+      </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="129">
-        <v>15.878443297426932</v>
-      </c>
-      <c r="C46" s="129">
-        <v>5.8132983192169343</v>
-      </c>
-      <c r="D46" s="129">
-        <v>1.5883417645147817</v>
-      </c>
-      <c r="E46" s="129"/>
-      <c r="F46" s="129">
-        <v>10.46983353378042</v>
+      <c r="B46" s="109">
+        <v>5.8435661546965711</v>
+      </c>
+      <c r="C46" s="109">
+        <v>8.3106833222568888</v>
+      </c>
+      <c r="D46" s="109">
+        <v>3.8128342245989297</v>
+      </c>
+      <c r="E46" s="109"/>
+      <c r="F46" s="109">
+        <v>89.613343442001479</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>133</v>
@@ -8409,8 +14067,18 @@
       <c r="H46" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I46" s="5">
+        <v>69.696396059999998</v>
+      </c>
+      <c r="J46" s="9">
+        <v>63</v>
+      </c>
+      <c r="K46" s="9">
+        <f t="shared" si="0"/>
+        <v>1.1062920009523809</v>
+      </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="50" t="s">
         <v>101</v>
       </c>
@@ -8429,8 +14097,27 @@
       <c r="H47" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I47" s="5">
+        <v>112.55085055666601</v>
+      </c>
+      <c r="J47" s="9">
+        <v>100</v>
+      </c>
+      <c r="K47" s="9">
+        <f t="shared" si="0"/>
+        <v>1.12550850556666</v>
+      </c>
+      <c r="AB47" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC47" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD47" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="50" t="s">
         <v>102</v>
       </c>
@@ -8449,8 +14136,75 @@
       <c r="H48" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I48" s="5">
+        <v>117.49299123</v>
+      </c>
+      <c r="J48" s="9">
+        <v>108</v>
+      </c>
+      <c r="K48" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0878980669444445</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="M48" s="9">
+        <f>AVERAGE(M33:M45)</f>
+        <v>21.511640463650565</v>
+      </c>
+      <c r="N48" s="9">
+        <f>AVERAGE(N33:N45)</f>
+        <v>7.9902055278750073</v>
+      </c>
+      <c r="O48" s="9">
+        <f>AVERAGE(O33:O45)</f>
+        <v>1.4642959076473792</v>
+      </c>
+      <c r="P48" s="9">
+        <f>AVERAGE(P33:P45)</f>
+        <v>2.0264453252093029</v>
+      </c>
+      <c r="Q48" s="9">
+        <f>AVERAGE(Q33:Q45)</f>
+        <v>20.563234527273458</v>
+      </c>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="U48" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V48" s="9">
+        <f>AVERAGE(V33:V38)</f>
+        <v>4.9703992696582953</v>
+      </c>
+      <c r="W48" s="9">
+        <f>AVERAGE(W33:W38)</f>
+        <v>5.2252215788013956</v>
+      </c>
+      <c r="X48" s="9">
+        <f>AVERAGE(X33:X38)</f>
+        <v>1.64536082059517</v>
+      </c>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="9">
+        <f>AVERAGE(Z33:Z38)</f>
+        <v>69.269648723780605</v>
+      </c>
+      <c r="AB48" s="9">
+        <f>M48/V48</f>
+        <v>4.3279501900316042</v>
+      </c>
+      <c r="AC48" s="9">
+        <f>N48/W48</f>
+        <v>1.5291610905633339</v>
+      </c>
+      <c r="AD48" s="9">
+        <f>O48/X48</f>
+        <v>0.88995428195361126</v>
+      </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="50" t="s">
         <v>103</v>
       </c>
@@ -8469,8 +14223,62 @@
       <c r="H49" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I49" s="5">
+        <v>115.079453056666</v>
+      </c>
+      <c r="J49" s="9">
+        <v>112</v>
+      </c>
+      <c r="K49" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0274951165773749</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="M49" s="7">
+        <v>13</v>
+      </c>
+      <c r="N49" s="7">
+        <v>8</v>
+      </c>
+      <c r="O49" s="7">
+        <v>13</v>
+      </c>
+      <c r="P49" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>5</v>
+      </c>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="U49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="V49" s="7">
+        <v>6</v>
+      </c>
+      <c r="W49" s="7">
+        <v>3</v>
+      </c>
+      <c r="X49" s="7">
+        <v>6</v>
+      </c>
+      <c r="Z49" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9">
+        <f t="shared" ref="AC49:AD51" si="1">N49/W49</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="AD49" s="9">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="50" t="s">
         <v>104</v>
       </c>
@@ -8489,8 +14297,76 @@
       <c r="H50" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="I50" s="5">
+        <v>119.222878299999</v>
+      </c>
+      <c r="J50" s="9">
+        <v>110</v>
+      </c>
+      <c r="K50" s="9">
+        <f t="shared" si="0"/>
+        <v>1.083844348181809</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="M50" s="9">
+        <f>MEDIAN(M33:M45)</f>
+        <v>16.772053867140858</v>
+      </c>
+      <c r="N50" s="9">
+        <f t="shared" ref="N50:Z50" si="2">MEDIAN(N33:N45)</f>
+        <v>5.5913524785725599</v>
+      </c>
+      <c r="O50" s="9">
+        <f t="shared" si="2"/>
+        <v>1.1846386681800984</v>
+      </c>
+      <c r="P50" s="9">
+        <f t="shared" si="2"/>
+        <v>2.0264453252093029</v>
+      </c>
+      <c r="Q50" s="9">
+        <f t="shared" si="2"/>
+        <v>25.469899999999999</v>
+      </c>
+      <c r="R50" s="9"/>
+      <c r="S50" s="9"/>
+      <c r="T50" s="9"/>
+      <c r="U50" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="V50" s="9">
+        <f t="shared" si="2"/>
+        <v>4.9617465097889522</v>
+      </c>
+      <c r="W50" s="9">
+        <f t="shared" si="2"/>
+        <v>5.1018819069872396</v>
+      </c>
+      <c r="X50" s="9">
+        <f t="shared" si="2"/>
+        <v>1.2637313853016972</v>
+      </c>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="9">
+        <f t="shared" si="2"/>
+        <v>69.269648723780605</v>
+      </c>
+      <c r="AB50" s="9">
+        <f t="shared" ref="AB50:AB56" si="3">M50/V50</f>
+        <v>3.3802722154490432</v>
+      </c>
+      <c r="AC50" s="9">
+        <f t="shared" si="1"/>
+        <v>1.0959392201757885</v>
+      </c>
+      <c r="AD50" s="9">
+        <f t="shared" si="1"/>
+        <v>0.93741334745538785</v>
+      </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="50" t="s">
         <v>105</v>
       </c>
@@ -8509,8 +14385,76 @@
       <c r="H51" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I51" s="5">
+        <v>115.360934813333</v>
+      </c>
+      <c r="J51" s="9">
+        <v>111</v>
+      </c>
+      <c r="K51" s="9">
+        <f t="shared" si="0"/>
+        <v>1.039287701021018</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="M51" s="9">
+        <f>GEOMEAN(M33:M45)</f>
+        <v>12.405966118447138</v>
+      </c>
+      <c r="N51" s="9">
+        <f t="shared" ref="N51:Z51" si="4">GEOMEAN(N33:N45)</f>
+        <v>6.7597359482998618</v>
+      </c>
+      <c r="O51" s="9">
+        <f t="shared" si="4"/>
+        <v>1.341323283549237</v>
+      </c>
+      <c r="P51" s="9">
+        <f t="shared" si="4"/>
+        <v>1.7472523144693801</v>
+      </c>
+      <c r="Q51" s="9">
+        <f t="shared" si="4"/>
+        <v>9.9113088829671874</v>
+      </c>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="V51" s="9">
+        <f t="shared" si="4"/>
+        <v>4.3993491051622939</v>
+      </c>
+      <c r="W51" s="9">
+        <f t="shared" si="4"/>
+        <v>4.5781525718330345</v>
+      </c>
+      <c r="X51" s="9">
+        <f t="shared" si="4"/>
+        <v>1.4622116175159132</v>
+      </c>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="9">
+        <f t="shared" si="4"/>
+        <v>66.214940304494675</v>
+      </c>
+      <c r="AB51" s="9">
+        <f t="shared" si="3"/>
+        <v>2.8199549119413372</v>
+      </c>
+      <c r="AC51" s="9">
+        <f t="shared" si="1"/>
+        <v>1.4765204615261105</v>
+      </c>
+      <c r="AD51" s="9">
+        <f t="shared" si="1"/>
+        <v>0.9173250078726306</v>
+      </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="50" t="s">
         <v>106</v>
       </c>
@@ -8529,8 +14473,21 @@
       <c r="H52" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I52" s="5">
+        <v>118.05576815000001</v>
+      </c>
+      <c r="J52" s="9">
+        <v>111</v>
+      </c>
+      <c r="K52" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0635654788288289</v>
+      </c>
+      <c r="AB52" s="9"/>
+      <c r="AC52" s="9"/>
+      <c r="AD52" s="9"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="50" t="s">
         <v>107</v>
       </c>
@@ -8549,8 +14506,21 @@
       <c r="H53" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I53" s="5">
+        <v>119.77022043333299</v>
+      </c>
+      <c r="J53" s="9">
+        <v>115</v>
+      </c>
+      <c r="K53" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0414801776811564</v>
+      </c>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9"/>
+      <c r="AD53" s="9"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="50" t="s">
         <v>108</v>
       </c>
@@ -8569,8 +14539,70 @@
       <c r="H54" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I54" s="5">
+        <v>125.17995179</v>
+      </c>
+      <c r="J54" s="9">
+        <v>119</v>
+      </c>
+      <c r="K54" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0519323679831933</v>
+      </c>
+      <c r="L54" t="s">
+        <v>143</v>
+      </c>
+      <c r="M54" s="9">
+        <f>AVERAGE(M33:M37)</f>
+        <v>42.213736443382871</v>
+      </c>
+      <c r="N54" s="9">
+        <f>AVERAGE(N33:N37)</f>
+        <v>7.4045802831264895</v>
+      </c>
+      <c r="O54" s="9">
+        <f>AVERAGE(O33:O37)</f>
+        <v>1.0197614517102151</v>
+      </c>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9">
+        <f>AVERAGE(Q33:Q37)</f>
+        <v>1.65983178191882</v>
+      </c>
+      <c r="R54" s="9"/>
+      <c r="S54" s="9"/>
+      <c r="T54" s="9"/>
+      <c r="U54" t="s">
+        <v>143</v>
+      </c>
+      <c r="V54" s="9">
+        <f>AVERAGE(V33)</f>
+        <v>9.1507251134754828</v>
+      </c>
+      <c r="W54" s="9">
+        <f>AVERAGE(W33)</f>
+        <v>2.2630995071600584</v>
+      </c>
+      <c r="X54" s="9">
+        <f>AVERAGE(X33)</f>
+        <v>1.3518355223464986</v>
+      </c>
+      <c r="Y54" s="9"/>
+      <c r="Z54" s="9"/>
+      <c r="AB54" s="9">
+        <f t="shared" si="3"/>
+        <v>4.6131575279447903</v>
+      </c>
+      <c r="AC54" s="9">
+        <f>N54/W54</f>
+        <v>3.2718756995437754</v>
+      </c>
+      <c r="AD54" s="9">
+        <f>O54/X54</f>
+        <v>0.75435319967042025</v>
+      </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="50" t="s">
         <v>109</v>
       </c>
@@ -8589,8 +14621,75 @@
       <c r="H55" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I55" s="5">
+        <v>128.631154973333</v>
+      </c>
+      <c r="J55" s="9">
+        <v>119</v>
+      </c>
+      <c r="K55" s="9">
+        <f t="shared" si="0"/>
+        <v>1.0809340754061596</v>
+      </c>
+      <c r="L55" t="s">
+        <v>144</v>
+      </c>
+      <c r="M55" s="9">
+        <f>AVERAGE(M38:M40)</f>
+        <v>16.839661832027371</v>
+      </c>
+      <c r="N55" s="9">
+        <f>AVERAGE(N38:N40)</f>
+        <v>8.9662476024558675</v>
+      </c>
+      <c r="O55" s="9">
+        <f>AVERAGE(O38:O40)</f>
+        <v>2.6464574417498814</v>
+      </c>
+      <c r="P55" s="9">
+        <f>AVERAGE(P38:P40)</f>
+        <v>2.0264453252093029</v>
+      </c>
+      <c r="Q55" s="9">
+        <f>AVERAGE(Q38:Q40)</f>
+        <v>33.165503024176559</v>
+      </c>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="U55" t="s">
+        <v>144</v>
+      </c>
+      <c r="V55" s="9">
+        <f>AVERAGE(V34:V35)</f>
+        <v>5.77826642895542</v>
+      </c>
+      <c r="W55" s="9">
+        <f>AVERAGE(W34:W35)</f>
+        <v>6.7062826146220642</v>
+      </c>
+      <c r="X55" s="9">
+        <f>AVERAGE(X34:X35)</f>
+        <v>2.554490134611838</v>
+      </c>
+      <c r="Y55" s="9"/>
+      <c r="Z55" s="9">
+        <f>AVERAGE(Z34:Z35)</f>
+        <v>69.269648723780605</v>
+      </c>
+      <c r="AB55" s="9">
+        <f>M55/V55</f>
+        <v>2.9143103799510333</v>
+      </c>
+      <c r="AC55" s="9">
+        <f>N55/W55</f>
+        <v>1.3369922083072194</v>
+      </c>
+      <c r="AD55" s="9">
+        <f>O55/X55</f>
+        <v>1.0360022166035956</v>
+      </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="50" t="s">
         <v>116</v>
       </c>
@@ -8609,8 +14708,1123 @@
       <c r="H56" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="I56" s="5">
+        <v>127.417386873333</v>
+      </c>
+      <c r="J56" s="9">
+        <v>123</v>
+      </c>
+      <c r="K56" s="9">
+        <f>I56/J56</f>
+        <v>1.0359137144173414</v>
+      </c>
+      <c r="L56" t="s">
+        <v>145</v>
+      </c>
+      <c r="M56" s="9">
+        <f>AVERAGE(M41:M45)</f>
+        <v>3.6127316628921933</v>
+      </c>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9">
+        <f>AVERAGE(O41:O45)</f>
+        <v>1.1995334431230433</v>
+      </c>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
+      <c r="R56" s="9"/>
+      <c r="S56" s="9"/>
+      <c r="U56" t="s">
+        <v>145</v>
+      </c>
+      <c r="V56" s="9">
+        <f>AVERAGE(V36:V38)</f>
+        <v>3.0383792155211502</v>
+      </c>
+      <c r="W56" s="9"/>
+      <c r="X56" s="9">
+        <f>AVERAGE(X36:X38)</f>
+        <v>1.137116377333615</v>
+      </c>
+      <c r="Y56" s="9"/>
+      <c r="Z56" s="9"/>
+      <c r="AB56" s="9">
+        <f t="shared" si="3"/>
+        <v>1.1890325093184686</v>
+      </c>
+      <c r="AC56" s="9"/>
+      <c r="AD56" s="9">
+        <f>O56/X56</f>
+        <v>1.054890657661433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC57" s="9"/>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C75" s="148" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" s="148"/>
+      <c r="E75" s="148" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" s="148"/>
+    </row>
+    <row r="76" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="117"/>
+      <c r="C76" s="134" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="135" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="134" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76" s="135" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" s="135" t="s">
+        <v>149</v>
+      </c>
+      <c r="H76" s="136" t="s">
+        <v>151</v>
+      </c>
+      <c r="I76" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="K76" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="U76" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B77" s="112" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="127">
+        <v>34.051098327464274</v>
+      </c>
+      <c r="D77" s="137">
+        <v>0.98018285608205336</v>
+      </c>
+      <c r="E77" s="5">
+        <f>LN(C77)</f>
+        <v>3.527862288388492</v>
+      </c>
+      <c r="F77" s="5">
+        <f>LN(D77)</f>
+        <v>-2.0016136884035245E-2</v>
+      </c>
+      <c r="G77" s="140">
+        <v>22.75</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="I77" s="9">
+        <v>1.8217360439061068</v>
+      </c>
+      <c r="K77" s="145" t="s">
+        <v>152</v>
+      </c>
+      <c r="L77" s="145"/>
+      <c r="U77" s="145" t="s">
+        <v>152</v>
+      </c>
+      <c r="V77" s="145"/>
+    </row>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="112" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="127">
+        <v>33.133326116946698</v>
+      </c>
+      <c r="D78" s="137">
+        <v>1.1171856871026129</v>
+      </c>
+      <c r="E78" s="5">
+        <f t="shared" ref="E78:E95" si="5">LN(C78)</f>
+        <v>3.5005396071960058</v>
+      </c>
+      <c r="F78" s="5">
+        <f t="shared" ref="F78:F95" si="6">LN(D78)</f>
+        <v>0.11081274360564797</v>
+      </c>
+      <c r="G78" s="141">
+        <v>21.992000000000001</v>
+      </c>
+      <c r="H78" s="2">
+        <v>1</v>
+      </c>
+      <c r="I78" s="9">
+        <v>1.7511459705059222</v>
+      </c>
+      <c r="K78" t="s">
+        <v>153</v>
+      </c>
+      <c r="L78">
+        <v>0.95236366409304141</v>
+      </c>
+      <c r="U78" t="s">
+        <v>153</v>
+      </c>
+      <c r="V78">
+        <v>0.2875750191067894</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="112" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="127">
+        <v>35.606836561802155</v>
+      </c>
+      <c r="D79" s="137">
+        <v>1.0759734533809813</v>
+      </c>
+      <c r="E79" s="5">
+        <f t="shared" si="5"/>
+        <v>3.5725376576738692</v>
+      </c>
+      <c r="F79" s="5">
+        <f t="shared" si="6"/>
+        <v>7.3225789856230572E-2</v>
+      </c>
+      <c r="G79" s="141">
+        <v>21.641999999999999</v>
+      </c>
+      <c r="H79" s="2">
+        <v>1</v>
+      </c>
+      <c r="I79" s="9">
+        <v>1.9502412933524087</v>
+      </c>
+      <c r="K79" t="s">
+        <v>154</v>
+      </c>
+      <c r="L79">
+        <v>0.90699654868472346</v>
+      </c>
+      <c r="U79" t="s">
+        <v>154</v>
+      </c>
+      <c r="V79">
+        <v>8.2699391614270298E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="127">
+        <v>58.672457292115254</v>
+      </c>
+      <c r="D80" s="137">
+        <v>0.85506102937763973</v>
+      </c>
+      <c r="E80" s="5">
+        <f t="shared" si="5"/>
+        <v>4.0719704053420118</v>
+      </c>
+      <c r="F80" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.1565824332037119</v>
+      </c>
+      <c r="G80" s="141">
+        <v>21.291</v>
+      </c>
+      <c r="H80" s="2">
+        <v>1</v>
+      </c>
+      <c r="I80" s="9">
+        <v>2.1366341811379534</v>
+      </c>
+      <c r="K80" t="s">
+        <v>155</v>
+      </c>
+      <c r="L80">
+        <v>0.89537111727031382</v>
+      </c>
+      <c r="U80" t="s">
+        <v>155</v>
+      </c>
+      <c r="V80">
+        <v>-3.1963184433945913E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B81" s="112" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="127">
+        <v>49.604963918585945</v>
+      </c>
+      <c r="D81" s="137">
+        <v>1.0704042326077878</v>
+      </c>
+      <c r="E81" s="5">
+        <f t="shared" si="5"/>
+        <v>3.9040909077270611</v>
+      </c>
+      <c r="F81" s="5">
+        <f t="shared" si="6"/>
+        <v>6.8036364614005113E-2</v>
+      </c>
+      <c r="G81" s="140">
+        <v>23.274999999999999</v>
+      </c>
+      <c r="H81" s="2">
+        <v>1</v>
+      </c>
+      <c r="I81" s="9">
+        <v>2.6045116113513167</v>
+      </c>
+      <c r="K81" t="s">
+        <v>156</v>
+      </c>
+      <c r="L81">
+        <v>5.6652061047070319</v>
+      </c>
+      <c r="U81" t="s">
+        <v>156</v>
+      </c>
+      <c r="V81">
+        <v>0.8435303568628868</v>
+      </c>
+    </row>
+    <row r="82" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="112" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="127">
+        <v>9.1507251134754828</v>
+      </c>
+      <c r="D82" s="137">
+        <v>1.3518355223464986</v>
+      </c>
+      <c r="E82" s="5">
+        <f t="shared" si="5"/>
+        <v>2.2138331235218924</v>
+      </c>
+      <c r="F82" s="5">
+        <f t="shared" si="6"/>
+        <v>0.30146331515103636</v>
+      </c>
+      <c r="G82" s="140">
+        <v>10.617000000000001</v>
+      </c>
+      <c r="H82" s="2">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9">
+        <v>1.1221084536248001</v>
+      </c>
+      <c r="K82" s="143" t="s">
+        <v>157</v>
+      </c>
+      <c r="L82" s="143">
+        <v>19</v>
+      </c>
+      <c r="U82" s="143" t="s">
+        <v>157</v>
+      </c>
+      <c r="V82" s="143">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B83" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="109">
+        <v>19.721931625435001</v>
+      </c>
+      <c r="D83" s="138">
+        <v>3.099500713266762</v>
+      </c>
+      <c r="E83" s="5">
+        <f t="shared" si="5"/>
+        <v>2.9817312969857115</v>
+      </c>
+      <c r="F83" s="5">
+        <f t="shared" si="6"/>
+        <v>1.1312410382829794</v>
+      </c>
+      <c r="G83" s="141">
+        <v>71.117321599999997</v>
+      </c>
+      <c r="H83" s="2">
+        <v>1</v>
+      </c>
+      <c r="I83" s="9">
+        <v>1.2053783322033897</v>
+      </c>
+    </row>
+    <row r="84" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="C84" s="109">
+        <v>16.772053867140858</v>
+      </c>
+      <c r="D84" s="138">
+        <v>3.0032097004279601</v>
+      </c>
+      <c r="E84" s="5">
+        <f t="shared" si="5"/>
+        <v>2.8197140410336745</v>
+      </c>
+      <c r="F84" s="5">
+        <f t="shared" si="6"/>
+        <v>1.0996816168755115</v>
+      </c>
+      <c r="G84" s="141">
+        <v>74.728308609999999</v>
+      </c>
+      <c r="H84" s="2">
+        <v>1</v>
+      </c>
+      <c r="I84" s="9">
+        <v>1.1861636287301587</v>
+      </c>
+      <c r="K84" t="s">
+        <v>158</v>
+      </c>
+      <c r="U84" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B85" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="C85" s="109">
+        <v>14.025000003506266</v>
+      </c>
+      <c r="D85" s="138">
+        <v>1.8366619115549219</v>
+      </c>
+      <c r="E85" s="5">
+        <f t="shared" si="5"/>
+        <v>2.6408414516587611</v>
+      </c>
+      <c r="F85" s="5">
+        <f t="shared" si="6"/>
+        <v>0.60794974550330128</v>
+      </c>
+      <c r="G85" s="141">
+        <v>79.767295559999994</v>
+      </c>
+      <c r="H85" s="2">
+        <v>1</v>
+      </c>
+      <c r="I85" s="9">
+        <v>1.2085953872727271</v>
+      </c>
+      <c r="K85" s="144"/>
+      <c r="L85" s="144" t="s">
+        <v>163</v>
+      </c>
+      <c r="M85" s="144" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" s="144" t="s">
+        <v>164</v>
+      </c>
+      <c r="O85" s="144" t="s">
+        <v>165</v>
+      </c>
+      <c r="P85" s="144" t="s">
+        <v>166</v>
+      </c>
+      <c r="U85" s="144"/>
+      <c r="V85" s="144" t="s">
+        <v>163</v>
+      </c>
+      <c r="W85" s="144" t="s">
+        <v>37</v>
+      </c>
+      <c r="X85" s="144" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y85" s="144" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z85" s="144" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B86" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86" s="109">
+        <v>5.7129667032142688</v>
+      </c>
+      <c r="D86" s="138">
+        <v>1.2961460446247464</v>
+      </c>
+      <c r="E86" s="5">
+        <f t="shared" si="5"/>
+        <v>1.7427384514764823</v>
+      </c>
+      <c r="F86" s="5">
+        <f t="shared" si="6"/>
+        <v>0.2593952803348446</v>
+      </c>
+      <c r="G86" s="141">
+        <v>68.631809730000001</v>
+      </c>
+      <c r="H86" s="2">
+        <v>0</v>
+      </c>
+      <c r="I86" s="9">
+        <v>1.0893938052380951</v>
+      </c>
+      <c r="K86" t="s">
+        <v>159</v>
+      </c>
+      <c r="L86">
+        <v>2</v>
+      </c>
+      <c r="M86">
+        <v>5007.9268980699544</v>
+      </c>
+      <c r="N86">
+        <v>2503.9634490349772</v>
+      </c>
+      <c r="O86">
+        <v>78.018313157868107</v>
+      </c>
+      <c r="P86">
+        <v>5.5974796399785972E-9</v>
+      </c>
+      <c r="U86" t="s">
+        <v>159</v>
+      </c>
+      <c r="V86">
+        <v>2</v>
+      </c>
+      <c r="W86">
+        <v>1.0263891414452093</v>
+      </c>
+      <c r="X86">
+        <v>0.51319457072260466</v>
+      </c>
+      <c r="Y86">
+        <v>0.7212413541057614</v>
+      </c>
+      <c r="Z86">
+        <v>0.50129509172605147</v>
+      </c>
+    </row>
+    <row r="87" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B87" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="109">
+        <v>5.8435661546965711</v>
+      </c>
+      <c r="D87" s="138">
+        <v>3.8128342245989297</v>
+      </c>
+      <c r="E87" s="5">
+        <f t="shared" si="5"/>
+        <v>1.7653412534011035</v>
+      </c>
+      <c r="F87" s="5">
+        <f t="shared" si="6"/>
+        <v>1.3383728035597091</v>
+      </c>
+      <c r="G87" s="141">
+        <v>69.696396059999998</v>
+      </c>
+      <c r="H87" s="2">
+        <v>0</v>
+      </c>
+      <c r="I87" s="9">
+        <v>1.1062920009523809</v>
+      </c>
+      <c r="K87" t="s">
+        <v>160</v>
+      </c>
+      <c r="L87">
+        <v>16</v>
+      </c>
+      <c r="M87">
+        <v>513.51296334095707</v>
+      </c>
+      <c r="N87">
+        <v>32.094560208809817</v>
+      </c>
+      <c r="U87" t="s">
+        <v>160</v>
+      </c>
+      <c r="V87">
+        <v>16</v>
+      </c>
+      <c r="W87">
+        <v>11.384695407187666</v>
+      </c>
+      <c r="X87">
+        <v>0.7115434629492291</v>
+      </c>
+    </row>
+    <row r="88" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" s="111">
+        <v>4.2105263163636364</v>
+      </c>
+      <c r="D88" s="139">
+        <v>1.2313167259786477</v>
+      </c>
+      <c r="E88" s="5">
+        <f t="shared" si="5"/>
+        <v>1.4375876556438048</v>
+      </c>
+      <c r="F88" s="5">
+        <f t="shared" si="6"/>
+        <v>0.20808410572397851</v>
+      </c>
+      <c r="G88" s="141">
+        <v>112.55085055666601</v>
+      </c>
+      <c r="H88" s="2">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9">
+        <v>1.12550850556666</v>
+      </c>
+      <c r="K88" s="143" t="s">
+        <v>161</v>
+      </c>
+      <c r="L88" s="143">
+        <v>18</v>
+      </c>
+      <c r="M88" s="143">
+        <v>5521.4398614109114</v>
+      </c>
+      <c r="N88" s="143"/>
+      <c r="O88" s="143"/>
+      <c r="P88" s="143"/>
+      <c r="U88" s="143" t="s">
+        <v>161</v>
+      </c>
+      <c r="V88" s="143">
+        <v>18</v>
+      </c>
+      <c r="W88" s="143">
+        <v>12.411084548632875</v>
+      </c>
+      <c r="X88" s="143"/>
+      <c r="Y88" s="143"/>
+      <c r="Z88" s="143"/>
+    </row>
+    <row r="89" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" s="111">
+        <v>3.0666666666666669</v>
+      </c>
+      <c r="D89" s="139">
+        <v>1.0897703549060542</v>
+      </c>
+      <c r="E89" s="5">
+        <f t="shared" si="5"/>
+        <v>1.120591195386885</v>
+      </c>
+      <c r="F89" s="5">
+        <f t="shared" si="6"/>
+        <v>8.5966990471723431E-2</v>
+      </c>
+      <c r="G89" s="141">
+        <v>117.49299123</v>
+      </c>
+      <c r="H89" s="2">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9">
+        <v>1.0878980669444445</v>
+      </c>
+    </row>
+    <row r="90" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B90" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="111">
+        <v>1.8379446635331478</v>
+      </c>
+      <c r="D90" s="139">
+        <v>1.0902620511161436</v>
+      </c>
+      <c r="E90" s="5">
+        <f t="shared" si="5"/>
+        <v>0.60864791658862405</v>
+      </c>
+      <c r="F90" s="5">
+        <f t="shared" si="6"/>
+        <v>8.6418081214291065E-2</v>
+      </c>
+      <c r="G90" s="141">
+        <v>119.222878299999</v>
+      </c>
+      <c r="H90" s="2">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9">
+        <v>1.083844348181809</v>
+      </c>
+      <c r="K90" s="144"/>
+      <c r="L90" s="144" t="s">
+        <v>167</v>
+      </c>
+      <c r="M90" s="144" t="s">
+        <v>156</v>
+      </c>
+      <c r="N90" s="144" t="s">
+        <v>168</v>
+      </c>
+      <c r="O90" s="144" t="s">
+        <v>169</v>
+      </c>
+      <c r="P90" s="144" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q90" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="R90" s="144" t="s">
+        <v>172</v>
+      </c>
+      <c r="S90" s="144" t="s">
+        <v>173</v>
+      </c>
+      <c r="U90" s="144"/>
+      <c r="V90" s="144" t="s">
+        <v>167</v>
+      </c>
+      <c r="W90" s="144" t="s">
+        <v>156</v>
+      </c>
+      <c r="X90" s="144" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y90" s="144" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z90" s="144" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA90" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB90" s="144" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC90" s="144" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="91" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B91" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C91" s="111">
+        <v>1.9732142856297192</v>
+      </c>
+      <c r="D91" s="139">
+        <v>1.1892573900504686</v>
+      </c>
+      <c r="E91" s="5">
+        <f t="shared" si="5"/>
+        <v>0.67966383017980103</v>
+      </c>
+      <c r="F91" s="5">
+        <f t="shared" si="6"/>
+        <v>0.17332907035380449</v>
+      </c>
+      <c r="G91" s="141">
+        <v>115.360934813333</v>
+      </c>
+      <c r="H91" s="2">
+        <v>1</v>
+      </c>
+      <c r="I91" s="9">
+        <v>1.039287701021018</v>
+      </c>
+      <c r="K91" t="s">
+        <v>162</v>
+      </c>
+      <c r="L91">
+        <v>-33.090252539605025</v>
+      </c>
+      <c r="M91">
+        <v>4.1614063801888959</v>
+      </c>
+      <c r="N91">
+        <v>-7.9516993815208652</v>
+      </c>
+      <c r="O91">
+        <v>5.9981788594590301E-7</v>
+      </c>
+      <c r="P91">
+        <v>-41.912039977180605</v>
+      </c>
+      <c r="Q91">
+        <v>-24.268465102029445</v>
+      </c>
+      <c r="R91">
+        <v>-41.912039977180605</v>
+      </c>
+      <c r="S91">
+        <v>-24.268465102029445</v>
+      </c>
+      <c r="U91" t="s">
+        <v>162</v>
+      </c>
+      <c r="V91">
+        <v>2.2220378414163133</v>
+      </c>
+      <c r="W91">
+        <v>0.6196195767733258</v>
+      </c>
+      <c r="X91">
+        <v>3.5861324023808194</v>
+      </c>
+      <c r="Y91">
+        <v>2.4705427054353148E-3</v>
+      </c>
+      <c r="Z91">
+        <v>0.90850301711330861</v>
+      </c>
+      <c r="AA91">
+        <v>3.5355726657193181</v>
+      </c>
+      <c r="AB91">
+        <v>0.90850301711330861</v>
+      </c>
+      <c r="AC91">
+        <v>3.5355726657193181</v>
+      </c>
+    </row>
+    <row r="92" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B92" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" s="111">
+        <v>2.3771106941838647</v>
+      </c>
+      <c r="D92" s="139">
+        <v>1.1846386681800984</v>
+      </c>
+      <c r="E92" s="5">
+        <f t="shared" si="5"/>
+        <v>0.86588575615529439</v>
+      </c>
+      <c r="F92" s="5">
+        <f t="shared" si="6"/>
+        <v>0.16943780672211656</v>
+      </c>
+      <c r="G92" s="141">
+        <v>118.05576815000001</v>
+      </c>
+      <c r="H92" s="2">
+        <v>1</v>
+      </c>
+      <c r="I92" s="9">
+        <v>1.0635654788288289</v>
+      </c>
+      <c r="K92" t="s">
+        <v>151</v>
+      </c>
+      <c r="L92">
+        <v>3.8133105241626515</v>
+      </c>
+      <c r="M92">
+        <v>3.0259420813010243</v>
+      </c>
+      <c r="N92">
+        <v>1.2602060521010015</v>
+      </c>
+      <c r="O92">
+        <v>0.22566548549606993</v>
+      </c>
+      <c r="P92">
+        <v>-2.6014001291239834</v>
+      </c>
+      <c r="Q92">
+        <v>10.228021177449286</v>
+      </c>
+      <c r="R92">
+        <v>-2.6014001291239834</v>
+      </c>
+      <c r="S92">
+        <v>10.228021177449286</v>
+      </c>
+      <c r="U92" t="s">
+        <v>151</v>
+      </c>
+      <c r="V92">
+        <v>1.178268137819552E-2</v>
+      </c>
+      <c r="W92">
+        <v>0.45055271714925144</v>
+      </c>
+      <c r="X92">
+        <v>2.6151615404180002E-2</v>
+      </c>
+      <c r="Y92">
+        <v>0.97945980630108842</v>
+      </c>
+      <c r="Z92">
+        <v>-0.94334641128503782</v>
+      </c>
+      <c r="AA92">
+        <v>0.96691177404142881</v>
+      </c>
+      <c r="AB92">
+        <v>-0.94334641128503782</v>
+      </c>
+      <c r="AC92">
+        <v>0.96691177404142881</v>
+      </c>
+    </row>
+    <row r="93" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C93" s="111">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="D93" s="139">
+        <v>1.3070266528210455</v>
+      </c>
+      <c r="E93" s="5">
+        <f t="shared" si="5"/>
+        <v>1.4996230464268938</v>
+      </c>
+      <c r="F93" s="5">
+        <f t="shared" si="6"/>
+        <v>0.26775482679915613</v>
+      </c>
+      <c r="G93" s="141">
+        <v>119.77022043333299</v>
+      </c>
+      <c r="H93" s="2">
+        <v>1</v>
+      </c>
+      <c r="I93" s="9">
+        <v>1.0414801776811564</v>
+      </c>
+      <c r="K93" s="143" t="s">
+        <v>176</v>
+      </c>
+      <c r="L93" s="143">
+        <v>34.521897375466793</v>
+      </c>
+      <c r="M93" s="143">
+        <v>3.1378561525808784</v>
+      </c>
+      <c r="N93" s="143">
+        <v>11.001746318763727</v>
+      </c>
+      <c r="O93" s="143">
+        <v>7.1637418352262036E-9</v>
+      </c>
+      <c r="P93" s="143">
+        <v>27.86993948941657</v>
+      </c>
+      <c r="Q93" s="143">
+        <v>41.173855261517019</v>
+      </c>
+      <c r="R93" s="143">
+        <v>27.86993948941657</v>
+      </c>
+      <c r="S93" s="143">
+        <v>41.173855261517019</v>
+      </c>
+      <c r="U93" s="143" t="s">
+        <v>176</v>
+      </c>
+      <c r="V93" s="143">
+        <v>-0.52305948493326049</v>
+      </c>
+      <c r="W93" s="143">
+        <v>0.46721635034103193</v>
+      </c>
+      <c r="X93" s="143">
+        <v>-1.1195230743775713</v>
+      </c>
+      <c r="Y93" s="143">
+        <v>0.27944235924887684</v>
+      </c>
+      <c r="Z93" s="143">
+        <v>-1.5135139019040285</v>
+      </c>
+      <c r="AA93" s="143">
+        <v>0.46739493203750748</v>
+      </c>
+      <c r="AB93" s="143">
+        <v>-1.5135139019040285</v>
+      </c>
+      <c r="AC93" s="143">
+        <v>0.46739493203750748</v>
+      </c>
+    </row>
+    <row r="94" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B94" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" s="111">
+        <v>7.2333333348616673</v>
+      </c>
+      <c r="D94" s="139">
+        <v>1.2011631885049607</v>
+      </c>
+      <c r="E94" s="5">
+        <f t="shared" si="5"/>
+        <v>1.9786999720895946</v>
+      </c>
+      <c r="F94" s="5">
+        <f t="shared" si="6"/>
+        <v>0.18329041105718638</v>
+      </c>
+      <c r="G94" s="141">
+        <v>128.631154973333</v>
+      </c>
+      <c r="H94" s="2">
+        <v>1</v>
+      </c>
+      <c r="I94" s="9">
+        <v>1.0809340754061596</v>
+      </c>
+    </row>
+    <row r="95" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B95" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" s="111">
+        <v>1.9999999997857143</v>
+      </c>
+      <c r="D95" s="139">
+        <v>1.115581316058643</v>
+      </c>
+      <c r="E95" s="5">
+        <f t="shared" si="5"/>
+        <v>0.69314718045280244</v>
+      </c>
+      <c r="F95" s="5">
+        <f t="shared" si="6"/>
+        <v>0.10937562874518658</v>
+      </c>
+      <c r="G95" s="141">
+        <v>127.417386873333</v>
+      </c>
+      <c r="H95" s="2">
+        <v>1</v>
+      </c>
+      <c r="I95" s="9">
+        <v>1.0359137144173414</v>
+      </c>
+    </row>
+    <row r="96" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="E96" s="142"/>
+      <c r="F96" s="142"/>
+    </row>
+    <row r="98" spans="13:31" x14ac:dyDescent="0.25">
+      <c r="M98" s="146"/>
+      <c r="N98" s="146"/>
+      <c r="W98" s="146"/>
+      <c r="X98" s="146"/>
+    </row>
+    <row r="106" spans="13:31" x14ac:dyDescent="0.25">
+      <c r="M106" s="147"/>
+      <c r="N106" s="147"/>
+      <c r="O106" s="147"/>
+      <c r="P106" s="147"/>
+      <c r="Q106" s="147"/>
+      <c r="R106" s="147"/>
+      <c r="W106" s="147"/>
+      <c r="X106" s="147"/>
+      <c r="Y106" s="147"/>
+      <c r="Z106" s="147"/>
+      <c r="AA106" s="147"/>
+      <c r="AB106" s="147"/>
+    </row>
+    <row r="111" spans="13:31" x14ac:dyDescent="0.25">
+      <c r="M111" s="147"/>
+      <c r="N111" s="147"/>
+      <c r="O111" s="147"/>
+      <c r="P111" s="147"/>
+      <c r="Q111" s="147"/>
+      <c r="R111" s="147"/>
+      <c r="S111" s="147"/>
+      <c r="T111" s="147"/>
+      <c r="U111" s="147"/>
+      <c r="W111" s="147"/>
+      <c r="X111" s="147"/>
+      <c r="Y111" s="147"/>
+      <c r="Z111" s="147"/>
+      <c r="AA111" s="147"/>
+      <c r="AB111" s="147"/>
+      <c r="AC111" s="147"/>
+      <c r="AD111" s="147"/>
+      <c r="AE111" s="147"/>
+    </row>
+    <row r="118" spans="13:28" x14ac:dyDescent="0.25">
+      <c r="M118" s="146"/>
+      <c r="N118" s="146"/>
+      <c r="W118" s="146"/>
+      <c r="X118" s="146"/>
+    </row>
+    <row r="126" spans="13:28" x14ac:dyDescent="0.25">
+      <c r="M126" s="147"/>
+      <c r="N126" s="147"/>
+      <c r="O126" s="147"/>
+      <c r="P126" s="147"/>
+      <c r="Q126" s="147"/>
+      <c r="R126" s="147"/>
+      <c r="W126" s="147"/>
+      <c r="X126" s="147"/>
+      <c r="Y126" s="147"/>
+      <c r="Z126" s="147"/>
+      <c r="AA126" s="147"/>
+      <c r="AB126" s="147"/>
+    </row>
+    <row r="131" spans="13:31" x14ac:dyDescent="0.25">
+      <c r="M131" s="147"/>
+      <c r="N131" s="147"/>
+      <c r="O131" s="147"/>
+      <c r="P131" s="147"/>
+      <c r="Q131" s="147"/>
+      <c r="R131" s="147"/>
+      <c r="S131" s="147"/>
+      <c r="T131" s="147"/>
+      <c r="U131" s="147"/>
+      <c r="W131" s="147"/>
+      <c r="X131" s="147"/>
+      <c r="Y131" s="147"/>
+      <c r="Z131" s="147"/>
+      <c r="AA131" s="147"/>
+      <c r="AB131" s="147"/>
+      <c r="AC131" s="147"/>
+      <c r="AD131" s="147"/>
+      <c r="AE131" s="147"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/concentration_summary.xlsx
+++ b/concentration_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89FEF24-39E1-415F-AB54-9C26884DFA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00897892-CEC7-4049-B4DB-F08E6D4C01A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="181">
   <si>
     <t>Bottle</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t xml:space="preserve">DOC </t>
+  </si>
+  <si>
+    <t>tpeak/tc</t>
   </si>
 </sst>
 </file>
@@ -895,7 +898,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1323,6 +1326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5263,8 +5267,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.58088829646316809"/>
-                  <c:y val="-0.19836866195408953"/>
+                  <c:x val="-0.33275624793068515"/>
+                  <c:y val="-2.8035858698083223E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -5328,10 +5332,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>('Summary '!$C$77:$C$81,'Summary '!$C$81,'Summary '!$C$83:$C$85,'Summary '!$C$91:$C$95)</c:f>
+              <c:f>('Summary '!$C$77:$C$81,'Summary '!$C$83:$C$85,'Summary '!$C$91:$C$95)</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>34.051098327464274</c:v>
                 </c:pt>
@@ -5348,30 +5352,27 @@
                   <c:v>49.604963918585945</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49.604963918585945</c:v>
+                  <c:v>19.721931625435001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.721931625435001</c:v>
+                  <c:v>16.772053867140858</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16.772053867140858</c:v>
+                  <c:v>14.025000003506266</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>14.025000003506266</c:v>
+                  <c:v>1.9732142856297192</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.9732142856297192</c:v>
+                  <c:v>2.3771106941838647</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3771106941838647</c:v>
+                  <c:v>4.4800000000000004</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.4800000000000004</c:v>
+                  <c:v>7.2333333348616673</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.2333333348616673</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>1.9999999997857143</c:v>
                 </c:pt>
               </c:numCache>
@@ -5410,8 +5411,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.48356726305482062"/>
-                  <c:y val="0.17386669237910232"/>
+                  <c:x val="0.50616971677054812"/>
+                  <c:y val="-0.11753253414540164"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -5501,6 +5502,7 @@
         <c:axId val="927164288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5563,7 +5565,6 @@
         <c:axId val="927161408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="25"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5631,6 +5632,539 @@
       </c:legendEntry>
       <c:legendEntry>
         <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:prstDash val="dash"/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>CF vs peak/base</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Natural Storms</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>natural storms</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.18425368982625664"/>
+                  <c:y val="-0.15104448915927224"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </c:spPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$J$83:$J$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.1737788669959504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0182769682576838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0331150820718804</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0275460447393339</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0275826446035865</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0831630031367767</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0183454205725238</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$83:$C$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7129667032142688</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8435661546965711</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2105263163636364</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8379446635331478</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A3BA-40C1-8A1C-ED183D64235F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>summer</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.3289408605117645E-2"/>
+                  <c:y val="-8.4956158968100021E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$J$83:$J$85</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.1737788669959504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0182769682576838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$83:$C$85</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>19.721931625435001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.772053867140858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.025000003506266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-A3BA-40C1-8A1C-ED183D64235F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>spring</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:trendline>
+            <c:spPr>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.18471873518125653"/>
+                  <c:y val="8.9829438829716862E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summary '!$J$91:$J$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0331150820718804</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0275460447393339</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0275826446035865</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0831630031367767</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0183454205725238</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summary '!$C$91:$C$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.9732142856297192</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3771106941838647</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.2333333348616673</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9999999997857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-A3BA-40C1-8A1C-ED183D64235F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927164288"/>
+        <c:axId val="927161408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927164288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927161408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927161408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927164288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:overlay val="0"/>
@@ -5933,16 +6467,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>46164</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>742680</xdr:colOff>
       <xdr:row>110</xdr:row>
-      <xdr:rowOff>144998</xdr:rowOff>
+      <xdr:rowOff>85467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>33323</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>46215</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>664355</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>177184</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5964,6 +6498,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>541734</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>489533</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>186966</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{778A45B0-6D6A-4DDC-BCD7-875B74444A40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15024,6 +15596,9 @@
       <c r="I82" s="9">
         <v>1.1221084536248001</v>
       </c>
+      <c r="J82" s="7" t="s">
+        <v>180</v>
+      </c>
       <c r="K82" s="143" t="s">
         <v>157</v>
       </c>
@@ -15064,6 +15639,9 @@
       <c r="I83" s="9">
         <v>1.2053783322033897</v>
       </c>
+      <c r="J83" s="14">
+        <v>1.1737788669959504</v>
+      </c>
     </row>
     <row r="84" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="62" t="s">
@@ -15092,6 +15670,9 @@
       <c r="I84" s="9">
         <v>1.1861636287301587</v>
       </c>
+      <c r="J84" s="14">
+        <v>1.0182769682576838</v>
+      </c>
       <c r="K84" t="s">
         <v>158</v>
       </c>
@@ -15126,6 +15707,9 @@
       <c r="I85" s="9">
         <v>1.2085953872727271</v>
       </c>
+      <c r="J85" s="14">
+        <v>1</v>
+      </c>
       <c r="K85" s="144"/>
       <c r="L85" s="144" t="s">
         <v>163</v>
@@ -15186,6 +15770,7 @@
       <c r="I86" s="9">
         <v>1.0893938052380951</v>
       </c>
+      <c r="J86" s="149"/>
       <c r="K86" t="s">
         <v>159</v>
       </c>
@@ -15250,6 +15835,7 @@
       <c r="I87" s="9">
         <v>1.1062920009523809</v>
       </c>
+      <c r="J87" s="149"/>
       <c r="K87" t="s">
         <v>160</v>
       </c>
@@ -15302,6 +15888,7 @@
       <c r="I88" s="9">
         <v>1.12550850556666</v>
       </c>
+      <c r="J88" s="149"/>
       <c r="K88" s="143" t="s">
         <v>161</v>
       </c>
@@ -15354,6 +15941,7 @@
       <c r="I89" s="9">
         <v>1.0878980669444445</v>
       </c>
+      <c r="J89" s="149"/>
     </row>
     <row r="90" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B90" s="50" t="s">
@@ -15382,6 +15970,7 @@
       <c r="I90" s="9">
         <v>1.083844348181809</v>
       </c>
+      <c r="J90" s="149"/>
       <c r="K90" s="144"/>
       <c r="L90" s="144" t="s">
         <v>167</v>
@@ -15460,6 +16049,9 @@
       <c r="I91" s="9">
         <v>1.039287701021018</v>
       </c>
+      <c r="J91" s="149">
+        <v>1.0331150820718804</v>
+      </c>
       <c r="K91" t="s">
         <v>162</v>
       </c>
@@ -15542,6 +16134,9 @@
       <c r="I92" s="9">
         <v>1.0635654788288289</v>
       </c>
+      <c r="J92" s="149">
+        <v>1.0275460447393339</v>
+      </c>
       <c r="K92" t="s">
         <v>151</v>
       </c>
@@ -15624,6 +16219,9 @@
       <c r="I93" s="9">
         <v>1.0414801776811564</v>
       </c>
+      <c r="J93" s="149">
+        <v>1.0275826446035865</v>
+      </c>
       <c r="K93" s="143" t="s">
         <v>176</v>
       </c>
@@ -15706,6 +16304,9 @@
       <c r="I94" s="9">
         <v>1.0809340754061596</v>
       </c>
+      <c r="J94" s="149">
+        <v>1.0831630031367767</v>
+      </c>
     </row>
     <row r="95" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B95" s="50" t="s">
@@ -15733,6 +16334,9 @@
       </c>
       <c r="I95" s="9">
         <v>1.0359137144173414</v>
+      </c>
+      <c r="J95" s="149">
+        <v>1.0183454205725238</v>
       </c>
     </row>
     <row r="96" spans="2:29" x14ac:dyDescent="0.25">
